--- a/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
   <si>
     <t>VRME</t>
   </si>
@@ -656,182 +656,189 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F8" s="3">
         <v>5600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>5300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>5700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>9700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>4500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>300</v>
       </c>
-      <c r="M8" s="3">
-        <v>100</v>
-      </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
+        <v>100</v>
+      </c>
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
-        <v>100</v>
-      </c>
-      <c r="P8" s="3">
-        <v>100</v>
-      </c>
       <c r="Q8" s="3">
         <v>100</v>
       </c>
@@ -845,10 +852,10 @@
         <v>100</v>
       </c>
       <c r="U8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -859,14 +866,14 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>4</v>
+      <c r="Z8" s="3">
+        <v>0</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
@@ -880,43 +887,49 @@
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>5600</v>
+      </c>
+      <c r="F9" s="3">
         <v>3300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>6900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>2800</v>
       </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>100</v>
-      </c>
       <c r="L9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9" s="3">
         <v>0</v>
@@ -951,11 +964,11 @@
       <c r="Y9" s="3">
         <v>0</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA9" s="3" t="s">
-        <v>4</v>
+      <c r="Z9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>0</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>4</v>
@@ -966,14 +979,20 @@
       <c r="AD9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE9" s="3">
-        <v>0</v>
+      <c r="AE9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -981,31 +1000,31 @@
         <v>2300</v>
       </c>
       <c r="E10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G10" s="3">
         <v>1800</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2800</v>
       </c>
       <c r="H10" s="3">
         <v>1800</v>
       </c>
       <c r="I10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K10" s="3">
         <v>1700</v>
-      </c>
-      <c r="J10" s="3">
-        <v>200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>200</v>
       </c>
       <c r="L10" s="3">
         <v>200</v>
       </c>
       <c r="M10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N10" s="3">
         <v>200</v>
@@ -1014,7 +1033,7 @@
         <v>100</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q10" s="3">
         <v>100</v>
@@ -1029,10 +1048,10 @@
         <v>100</v>
       </c>
       <c r="U10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W10" s="3">
         <v>0</v>
@@ -1043,11 +1062,11 @@
       <c r="Y10" s="3">
         <v>0</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA10" s="3" t="s">
-        <v>4</v>
+      <c r="Z10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="3">
+        <v>0</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>4</v>
@@ -1058,14 +1077,20 @@
       <c r="AD10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE10" s="3">
-        <v>0</v>
+      <c r="AE10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,16 +1123,18 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12" s="3">
         <v>0</v>
@@ -1145,41 +1172,41 @@
       <c r="Q12" s="3">
         <v>0</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0</v>
+      <c r="R12" s="3">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V12" s="3">
         <v>0</v>
       </c>
       <c r="W12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="3">
         <v>0</v>
       </c>
       <c r="AC12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
@@ -1187,11 +1214,17 @@
       <c r="AE12" s="3">
         <v>0</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,46 +1315,52 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K14" s="3">
-        <v>100</v>
-      </c>
-      <c r="L14" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14" s="3">
         <v>100</v>
       </c>
       <c r="O14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P14" s="3">
         <v>100</v>
@@ -1330,52 +1369,58 @@
         <v>100</v>
       </c>
       <c r="R14" s="3">
+        <v>100</v>
+      </c>
+      <c r="S14" s="3">
+        <v>100</v>
+      </c>
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
-        <v>100</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>100</v>
       </c>
       <c r="V14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W14" s="3">
         <v>100</v>
       </c>
       <c r="X14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y14" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z14" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>200</v>
       </c>
       <c r="AB14" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="AC14" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AD14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE14" s="3">
         <v>100</v>
       </c>
       <c r="AF14" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1397,11 +1442,11 @@
       <c r="I15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="J15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1412,11 +1457,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>4</v>
@@ -1430,11 +1475,11 @@
       <c r="T15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U15" s="3">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3">
-        <v>0</v>
+      <c r="U15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W15" s="3">
         <v>0</v>
@@ -1466,8 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F17" s="3">
         <v>6500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>6400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>7200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>5800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1000</v>
-      </c>
-      <c r="S17" s="3">
-        <v>700</v>
-      </c>
-      <c r="T17" s="3">
-        <v>700</v>
       </c>
       <c r="U17" s="3">
         <v>700</v>
       </c>
       <c r="V17" s="3">
+        <v>700</v>
+      </c>
+      <c r="W17" s="3">
+        <v>700</v>
+      </c>
+      <c r="X17" s="3">
         <v>600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>2800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>100</v>
+      </c>
+      <c r="F18" s="3">
         <v>-900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1500</v>
       </c>
-      <c r="G18" s="3">
-        <v>100</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-1300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-1600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-1100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-1000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-1100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-600</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-700</v>
       </c>
       <c r="V18" s="3">
         <v>-600</v>
       </c>
       <c r="W18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="X18" s="3">
         <v>-600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-800</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,44 +1780,46 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>200</v>
       </c>
       <c r="F20" s="3">
         <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-11200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
-        <v>100</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>100</v>
+      </c>
+      <c r="N20" s="3">
         <v>8200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1760,23 +1827,23 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -1786,121 +1853,133 @@
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>4</v>
+      <c r="Z20" s="3">
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-300</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-12300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>7200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-1200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-1100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-2600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-700</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-500</v>
       </c>
       <c r="X21" s="3">
         <v>-500</v>
       </c>
       <c r="Y21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-800</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-600</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1952,11 +2031,11 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>4</v>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>4</v>
@@ -1970,11 +2049,11 @@
       <c r="Y22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>200</v>
+      <c r="Z22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
@@ -1983,108 +2062,120 @@
         <v>200</v>
       </c>
       <c r="AD22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1600</v>
       </c>
-      <c r="G23" s="3">
-        <v>100</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>100</v>
+      </c>
+      <c r="J23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-12600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>7200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-2700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-700</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-500</v>
       </c>
       <c r="X23" s="3">
         <v>-500</v>
       </c>
       <c r="Y23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-300</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2109,17 +2200,17 @@
       <c r="J24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>4</v>
+      <c r="K24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>4</v>
@@ -2133,11 +2224,11 @@
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -2175,8 +2266,14 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1600</v>
       </c>
-      <c r="G26" s="3">
-        <v>100</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-12600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>7200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-1200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-700</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-500</v>
       </c>
       <c r="X26" s="3">
         <v>-500</v>
       </c>
       <c r="Y26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-300</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1600</v>
       </c>
-      <c r="G27" s="3">
-        <v>100</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-12600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-1400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-1000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>7200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-2700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-700</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-500</v>
       </c>
       <c r="X27" s="3">
         <v>-500</v>
       </c>
       <c r="Y27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-300</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2756,14 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,44 +2952,50 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
-        <v>100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>11200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-8200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2864,22 +3003,22 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>1900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>100</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W32" s="3">
         <v>0</v>
@@ -2890,121 +3029,133 @@
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>4</v>
+      <c r="Z32" s="3">
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="3">
         <v>300</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1600</v>
       </c>
-      <c r="G33" s="3">
-        <v>100</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>100</v>
+      </c>
+      <c r="J33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-12600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-1400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-1000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>7200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-2700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-700</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-500</v>
       </c>
       <c r="X33" s="3">
         <v>-500</v>
       </c>
       <c r="Y33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-300</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1600</v>
       </c>
-      <c r="G35" s="3">
-        <v>100</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>100</v>
+      </c>
+      <c r="J35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-12600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-1400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-1000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>7200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-2700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-700</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-500</v>
       </c>
       <c r="X35" s="3">
         <v>-500</v>
       </c>
       <c r="Y35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-300</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3523,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F41" s="3">
         <v>3000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>3100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>3400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>9400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>15400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>9600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>1100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>1700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>2100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>2300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>2300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>500</v>
       </c>
-      <c r="AD41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>0</v>
-      </c>
       <c r="AF41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3461,20 +3640,20 @@
       <c r="G42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H42" s="3">
-        <v>100</v>
-      </c>
-      <c r="I42" s="3">
-        <v>100</v>
+      <c r="H42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J42" s="3">
         <v>100</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
+      <c r="K42" s="3">
+        <v>100</v>
+      </c>
+      <c r="L42" s="3">
+        <v>100</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>4</v>
@@ -3485,11 +3664,11 @@
       <c r="O42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -3536,50 +3715,56 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F43" s="3">
         <v>2300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>5600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>100</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3587,16 +3772,16 @@
         <v>100</v>
       </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
         <v>100</v>
       </c>
       <c r="U43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
@@ -3607,11 +3792,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA43" s="3" t="s">
-        <v>4</v>
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3">
+        <v>0</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>4</v>
@@ -3628,8 +3813,14 @@
       <c r="AF43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3640,10 +3831,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H44" s="3">
         <v>100</v>
@@ -3658,7 +3849,7 @@
         <v>100</v>
       </c>
       <c r="L44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" s="3">
         <v>100</v>
@@ -3673,7 +3864,7 @@
         <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3718,10 +3909,16 @@
         <v>0</v>
       </c>
       <c r="AF44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3732,61 +3929,61 @@
         <v>300</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G45" s="3">
         <v>300</v>
       </c>
       <c r="H45" s="3">
+        <v>400</v>
+      </c>
+      <c r="I45" s="3">
+        <v>300</v>
+      </c>
+      <c r="J45" s="3">
         <v>200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>300</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
       </c>
       <c r="L45" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N45" s="3">
+        <v>100</v>
+      </c>
+      <c r="O45" s="3">
+        <v>100</v>
+      </c>
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T45" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="U45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>200</v>
       </c>
       <c r="W45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Y45" s="3">
         <v>0</v>
@@ -3809,114 +4006,126 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F46" s="3">
         <v>5600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>5900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>9500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>6000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>6500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>9100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>10000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>14600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>15800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>8200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>9200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>9700</v>
-      </c>
-      <c r="R46" s="3">
-        <v>1000</v>
-      </c>
-      <c r="S46" s="3">
-        <v>400</v>
       </c>
       <c r="T46" s="3">
         <v>1000</v>
       </c>
       <c r="U46" s="3">
+        <v>400</v>
+      </c>
+      <c r="V46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W46" s="3">
         <v>800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>2200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>2400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>600</v>
       </c>
-      <c r="AD46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>0</v>
-      </c>
       <c r="AF46" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>4</v>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
+        <v>0</v>
       </c>
       <c r="G47" s="3">
         <v>0</v>
@@ -3928,22 +4137,22 @@
         <v>0</v>
       </c>
       <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>11200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>11000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>10800</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>4</v>
+      <c r="O47" s="3">
+        <v>0</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>4</v>
@@ -3957,11 +4166,11 @@
       <c r="S47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3996,34 +4205,40 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>700</v>
+      </c>
+      <c r="F48" s="3">
         <v>800</v>
-      </c>
-      <c r="E48" s="3">
-        <v>800</v>
-      </c>
-      <c r="F48" s="3">
-        <v>900</v>
       </c>
       <c r="G48" s="3">
         <v>800</v>
       </c>
       <c r="H48" s="3">
+        <v>900</v>
+      </c>
+      <c r="I48" s="3">
         <v>800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
+        <v>800</v>
+      </c>
+      <c r="K48" s="3">
         <v>900</v>
-      </c>
-      <c r="J48" s="3">
-        <v>200</v>
-      </c>
-      <c r="K48" s="3">
-        <v>200</v>
       </c>
       <c r="L48" s="3">
         <v>200</v>
@@ -4049,11 +4264,11 @@
       <c r="S48" s="3">
         <v>200</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>4</v>
+      <c r="T48" s="3">
+        <v>200</v>
+      </c>
+      <c r="U48" s="3">
+        <v>200</v>
       </c>
       <c r="V48" s="3" t="s">
         <v>4</v>
@@ -4073,11 +4288,11 @@
       <c r="AA48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD48" s="3">
         <v>0</v>
@@ -4088,34 +4303,40 @@
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>12400</v>
+        <v>12000</v>
       </c>
       <c r="E49" s="3">
         <v>12300</v>
       </c>
       <c r="F49" s="3">
+        <v>12400</v>
+      </c>
+      <c r="G49" s="3">
+        <v>12300</v>
+      </c>
+      <c r="H49" s="3">
         <v>12500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>10400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>10500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>10600</v>
-      </c>
-      <c r="J49" s="3">
-        <v>500</v>
-      </c>
-      <c r="K49" s="3">
-        <v>500</v>
       </c>
       <c r="L49" s="3">
         <v>500</v>
@@ -4124,16 +4345,16 @@
         <v>500</v>
       </c>
       <c r="N49" s="3">
+        <v>500</v>
+      </c>
+      <c r="O49" s="3">
+        <v>500</v>
+      </c>
+      <c r="P49" s="3">
         <v>400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>400</v>
-      </c>
-      <c r="P49" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>300</v>
       </c>
       <c r="R49" s="3">
         <v>300</v>
@@ -4142,22 +4363,22 @@
         <v>300</v>
       </c>
       <c r="T49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U49" s="3">
         <v>300</v>
       </c>
       <c r="V49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W49" s="3">
         <v>300</v>
       </c>
       <c r="X49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Y49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Z49" s="3">
         <v>200</v>
@@ -4180,8 +4401,14 @@
       <c r="AF49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,34 +4597,40 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
-        <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>100</v>
-      </c>
       <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>4</v>
+      <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
+        <v>100</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>4</v>
@@ -4405,11 +4644,11 @@
       <c r="O52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>20700</v>
+      </c>
+      <c r="F54" s="3">
         <v>18800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>18400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>19400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>20800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>17400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>18100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>20900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>21700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>22600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>15300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>16500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>8800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>9800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>10300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>800</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>300</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>300</v>
       </c>
       <c r="AF54" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH54" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,40 +4967,42 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>500</v>
-      </c>
-      <c r="L57" s="3">
-        <v>400</v>
-      </c>
-      <c r="M57" s="3">
-        <v>400</v>
       </c>
       <c r="N57" s="3">
         <v>400</v>
@@ -4750,13 +5011,13 @@
         <v>400</v>
       </c>
       <c r="P57" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q57" s="3">
         <v>400</v>
       </c>
       <c r="R57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
@@ -4780,13 +5041,13 @@
         <v>400</v>
       </c>
       <c r="Z57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB57" s="3">
         <v>500</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>900</v>
       </c>
       <c r="AC57" s="3">
         <v>1000</v>
@@ -4795,39 +5056,45 @@
         <v>900</v>
       </c>
       <c r="AE57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF57" s="3">
         <v>900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="E58" s="3">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="F58" s="3">
         <v>1000</v>
       </c>
       <c r="G58" s="3">
-        <v>500</v>
+        <v>1300</v>
       </c>
       <c r="H58" s="3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>4</v>
+      <c r="J58" s="3">
+        <v>500</v>
+      </c>
+      <c r="K58" s="3">
+        <v>500</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>4</v>
@@ -4838,11 +5105,11 @@
       <c r="N58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -4851,28 +5118,28 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>100</v>
@@ -4884,16 +5151,22 @@
         <v>100</v>
       </c>
       <c r="AD58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF58" s="3">
         <v>200</v>
       </c>
-      <c r="AE58" s="3">
-        <v>100</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4901,26 +5174,26 @@
         <v>1100</v>
       </c>
       <c r="E59" s="3">
-        <v>1000</v>
+        <v>1300</v>
       </c>
       <c r="F59" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="G59" s="3">
         <v>1000</v>
       </c>
       <c r="H59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J59" s="3">
         <v>600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>700</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
@@ -4930,94 +5203,100 @@
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O59" s="3">
-        <v>0</v>
-      </c>
-      <c r="P59" s="3">
-        <v>0</v>
+      <c r="O59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q59" s="3">
         <v>0</v>
       </c>
       <c r="R59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S59" s="3">
+        <v>0</v>
+      </c>
+      <c r="T59" s="3">
+        <v>100</v>
+      </c>
+      <c r="U59" s="3">
         <v>300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>300</v>
       </c>
-      <c r="U59" s="3">
-        <v>100</v>
-      </c>
-      <c r="V59" s="3">
-        <v>100</v>
-      </c>
       <c r="W59" s="3">
         <v>100</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>4</v>
+      <c r="X59" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>100</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>100</v>
+      <c r="AA59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD59" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AE59" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="AF59" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AH59" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5100</v>
+      </c>
+      <c r="F60" s="3">
         <v>3600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>500</v>
-      </c>
-      <c r="L60" s="3">
-        <v>400</v>
-      </c>
-      <c r="M60" s="3">
-        <v>400</v>
       </c>
       <c r="N60" s="3">
         <v>400</v>
@@ -5026,85 +5305,91 @@
         <v>400</v>
       </c>
       <c r="P60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q60" s="3">
         <v>400</v>
       </c>
       <c r="R60" s="3">
+        <v>500</v>
+      </c>
+      <c r="S60" s="3">
+        <v>400</v>
+      </c>
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>500</v>
-      </c>
-      <c r="W60" s="3">
-        <v>500</v>
-      </c>
-      <c r="X60" s="3">
-        <v>400</v>
       </c>
       <c r="Y60" s="3">
         <v>500</v>
       </c>
       <c r="Z60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB60" s="3">
         <v>600</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>1000</v>
       </c>
       <c r="AC60" s="3">
         <v>1100</v>
       </c>
       <c r="AD60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF60" s="3">
         <v>1700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>1600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1500</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -5112,10 +5397,10 @@
         <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>100</v>
@@ -5127,10 +5412,10 @@
         <v>100</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -5168,43 +5453,49 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F62" s="3">
         <v>1200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>400</v>
       </c>
       <c r="I62" s="3">
         <v>400</v>
       </c>
       <c r="J62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="M62" s="3">
+        <v>100</v>
+      </c>
+      <c r="N62" s="3">
+        <v>0</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>4</v>
@@ -5218,11 +5509,11 @@
       <c r="R62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
-        <v>0</v>
+      <c r="S62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U62" s="3">
         <v>0</v>
@@ -5254,14 +5545,20 @@
       <c r="AD62" s="3">
         <v>0</v>
       </c>
-      <c r="AE62" s="3" t="s">
-        <v>4</v>
+      <c r="AE62" s="3">
+        <v>0</v>
       </c>
       <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F66" s="3">
         <v>6900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>500</v>
-      </c>
-      <c r="O66" s="3">
-        <v>500</v>
-      </c>
-      <c r="P66" s="3">
-        <v>600</v>
       </c>
       <c r="Q66" s="3">
         <v>500</v>
       </c>
       <c r="R66" s="3">
+        <v>600</v>
+      </c>
+      <c r="S66" s="3">
+        <v>500</v>
+      </c>
+      <c r="T66" s="3">
         <v>700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>500</v>
-      </c>
-      <c r="W66" s="3">
-        <v>500</v>
-      </c>
-      <c r="X66" s="3">
-        <v>400</v>
       </c>
       <c r="Y66" s="3">
         <v>500</v>
       </c>
       <c r="Z66" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB66" s="3">
         <v>600</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>1000</v>
       </c>
       <c r="AC66" s="3">
         <v>1100</v>
       </c>
       <c r="AD66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF66" s="3">
         <v>1700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-82400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-81800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-81900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-80900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-80000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-78500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-78600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-78000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-65500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-64100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-63100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-70200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-68900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-67700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-66500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-65500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-62900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-61800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-61100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-60400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-59800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-59300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-58700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-58200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-57500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-42800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-42500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-41900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-41600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F76" s="3">
         <v>11900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>12400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>13000</v>
-      </c>
-      <c r="G76" s="3">
-        <v>13600</v>
-      </c>
-      <c r="H76" s="3">
-        <v>13200</v>
       </c>
       <c r="I76" s="3">
         <v>13600</v>
       </c>
       <c r="J76" s="3">
+        <v>13200</v>
+      </c>
+      <c r="K76" s="3">
+        <v>13600</v>
+      </c>
+      <c r="L76" s="3">
         <v>20200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>21200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>22200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>14900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>16000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>8300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>9100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>9800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1600</v>
-      </c>
-      <c r="X76" s="3">
-        <v>2000</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>2000</v>
       </c>
       <c r="Z76" s="3">
         <v>2000</v>
       </c>
       <c r="AA76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AB76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC76" s="3">
         <v>-200</v>
       </c>
-      <c r="AB76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE76" s="3">
         <v>-300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1600</v>
       </c>
-      <c r="G81" s="3">
-        <v>100</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>100</v>
+      </c>
+      <c r="J81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-12600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-1400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-1000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>7200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-2700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-700</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-500</v>
       </c>
       <c r="X81" s="3">
         <v>-500</v>
       </c>
       <c r="Y81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-300</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6826,14 +7223,14 @@
         <v>300</v>
       </c>
       <c r="I83" s="3">
+        <v>300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>300</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -6888,17 +7285,23 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>4</v>
+      <c r="AD83" s="3">
+        <v>0</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,8 +7784,14 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7366,91 +7799,97 @@
         <v>-100</v>
       </c>
       <c r="E89" s="3">
-        <v>-300</v>
+        <v>800</v>
       </c>
       <c r="F89" s="3">
         <v>-100</v>
       </c>
       <c r="G89" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I89" s="3">
+        <v>100</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-400</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-200</v>
       </c>
       <c r="T89" s="3">
         <v>-300</v>
       </c>
       <c r="U89" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="V89" s="3">
-        <v>-600</v>
+        <v>-300</v>
       </c>
       <c r="W89" s="3">
         <v>-400</v>
       </c>
       <c r="X89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AA89" s="3">
         <v>-600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,43 +7922,45 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
       </c>
       <c r="G91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N91" s="3" t="s">
-        <v>4</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>4</v>
@@ -7530,17 +7971,17 @@
       <c r="Q91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>4</v>
@@ -7551,11 +7992,11 @@
       <c r="X91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -7575,8 +8016,14 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,64 +8212,70 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-7600</v>
       </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
+        <v>0</v>
+      </c>
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-3000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
       <c r="R94" s="3">
         <v>0</v>
       </c>
       <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-200</v>
-      </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-100</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -7828,7 +8287,7 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -7836,23 +8295,29 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8738,112 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F100" s="3">
         <v>700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
-        <v>100</v>
-      </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
+        <v>100</v>
+      </c>
+      <c r="K100" s="3">
         <v>4500</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>8400</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>9100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>500</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>2600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>1600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>800</v>
       </c>
-      <c r="AD100" s="3">
-        <v>100</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>100</v>
-      </c>
       <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8359,11 +8856,11 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>4</v>
@@ -8377,11 +8874,11 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-4000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>7400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>8700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
-        <v>100</v>
-      </c>
-      <c r="U102" s="3">
-        <v>-500</v>
-      </c>
       <c r="V102" s="3">
-        <v>-600</v>
+        <v>100</v>
       </c>
       <c r="W102" s="3">
         <v>-500</v>
       </c>
       <c r="X102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>1600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>500</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>VRME</t>
   </si>
@@ -656,192 +656,196 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200</v>
-      </c>
-      <c r="M8" s="3">
-        <v>300</v>
       </c>
       <c r="N8" s="3">
         <v>300</v>
       </c>
       <c r="O8" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P8" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3">
-        <v>100</v>
-      </c>
       <c r="R8" s="3">
         <v>100</v>
       </c>
@@ -858,7 +862,7 @@
         <v>100</v>
       </c>
       <c r="W8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
@@ -872,11 +876,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -893,46 +897,49 @@
       <c r="AH8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E9" s="3">
         <v>3500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3300</v>
       </c>
-      <c r="G9" s="3">
-        <v>3500</v>
-      </c>
       <c r="H9" s="3">
+        <v>3700</v>
+      </c>
+      <c r="I9" s="3">
         <v>3900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2800</v>
       </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
       <c r="M9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3">
         <v>100</v>
       </c>
       <c r="O9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9" s="3">
         <v>0</v>
@@ -970,8 +977,8 @@
       <c r="AA9" s="3">
         <v>0</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>4</v>
+      <c r="AB9" s="3">
+        <v>0</v>
       </c>
       <c r="AC9" s="3" t="s">
         <v>4</v>
@@ -985,43 +992,46 @@
       <c r="AF9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E10" s="3">
         <v>2300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I10" s="3">
         <v>1800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K10" s="3">
         <v>1800</v>
       </c>
-      <c r="I10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1700</v>
-      </c>
-      <c r="L10" s="3">
-        <v>200</v>
       </c>
       <c r="M10" s="3">
         <v>200</v>
@@ -1030,14 +1040,14 @@
         <v>200</v>
       </c>
       <c r="O10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="P10" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q10" s="3">
         <v>200</v>
       </c>
-      <c r="Q10" s="3">
-        <v>100</v>
-      </c>
       <c r="R10" s="3">
         <v>100</v>
       </c>
@@ -1054,7 +1064,7 @@
         <v>100</v>
       </c>
       <c r="W10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X10" s="3">
         <v>0</v>
@@ -1068,8 +1078,8 @@
       <c r="AA10" s="3">
         <v>0</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>4</v>
+      <c r="AB10" s="3">
+        <v>0</v>
       </c>
       <c r="AC10" s="3" t="s">
         <v>4</v>
@@ -1083,14 +1093,17 @@
       <c r="AF10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,19 +1138,20 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E12" s="3">
         <v>100</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
@@ -1178,14 +1192,14 @@
       <c r="S12" s="3">
         <v>0</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>4</v>
+      <c r="T12" s="3">
+        <v>0</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V12" s="3">
-        <v>0</v>
+      <c r="V12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W12" s="3">
         <v>0</v>
@@ -1194,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="Y12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="3">
         <v>100</v>
       </c>
       <c r="AA12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB12" s="3">
         <v>0</v>
       </c>
       <c r="AC12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE12" s="3">
         <v>0</v>
@@ -1220,11 +1234,14 @@
       <c r="AG12" s="3">
         <v>0</v>
       </c>
-      <c r="AH12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,49 +1338,52 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>4</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M14" s="3">
-        <v>100</v>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N14" s="3">
         <v>100</v>
       </c>
       <c r="O14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="3">
         <v>100</v>
@@ -1375,16 +1395,16 @@
         <v>100</v>
       </c>
       <c r="T14" s="3">
+        <v>100</v>
+      </c>
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
-        <v>100</v>
-      </c>
       <c r="V14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X14" s="3">
         <v>100</v>
@@ -1393,34 +1413,37 @@
         <v>100</v>
       </c>
       <c r="Z14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>200</v>
       </c>
-      <c r="AD14" s="3">
-        <v>100</v>
-      </c>
       <c r="AE14" s="3">
         <v>100</v>
       </c>
       <c r="AF14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1448,8 +1471,8 @@
       <c r="K15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1463,8 +1486,8 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>4</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>4</v>
@@ -1481,8 +1504,8 @@
       <c r="V15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X15" s="3">
         <v>0</v>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,64 +1576,65 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E17" s="3">
         <v>6400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9600</v>
-      </c>
-      <c r="J17" s="3">
-        <v>5800</v>
       </c>
       <c r="K17" s="3">
         <v>5800</v>
       </c>
       <c r="L17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="M17" s="3">
         <v>1800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1000</v>
-      </c>
-      <c r="U17" s="3">
-        <v>700</v>
       </c>
       <c r="V17" s="3">
         <v>700</v>
@@ -1616,138 +1643,144 @@
         <v>700</v>
       </c>
       <c r="X17" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Y17" s="3">
         <v>600</v>
       </c>
       <c r="Z17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA17" s="3">
         <v>500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-600</v>
       </c>
-      <c r="E18" s="3">
-        <v>100</v>
-      </c>
       <c r="F18" s="3">
+        <v>100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1500</v>
       </c>
-      <c r="I18" s="3">
-        <v>100</v>
-      </c>
       <c r="J18" s="3">
+        <v>100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-900</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-600</v>
       </c>
       <c r="V18" s="3">
         <v>-600</v>
       </c>
       <c r="W18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X18" s="3">
         <v>-700</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-600</v>
       </c>
       <c r="Y18" s="3">
         <v>-600</v>
       </c>
       <c r="Z18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-800</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,8 +1815,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1791,38 +1825,38 @@
         <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
         <v>-100</v>
       </c>
       <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-11200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
-        <v>100</v>
-      </c>
       <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
         <v>8200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1833,20 +1867,20 @@
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
@@ -1859,94 +1893,97 @@
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>1200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>300</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-600</v>
       </c>
       <c r="G21" s="3">
         <v>-600</v>
       </c>
       <c r="H21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-1400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-1000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-2600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-600</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-700</v>
       </c>
       <c r="W21" s="3">
         <v>-700</v>
       </c>
       <c r="X21" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Y21" s="3">
         <v>-500</v>
@@ -1955,31 +1992,34 @@
         <v>-500</v>
       </c>
       <c r="AA21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-800</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-600</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG21" s="3">
-        <v>100</v>
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2037,8 +2077,8 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>4</v>
+      <c r="V22" s="3">
+        <v>0</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>4</v>
@@ -2055,94 +2095,97 @@
       <c r="AA22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="3">
         <v>200</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>200</v>
       </c>
-      <c r="AF22" s="3">
-        <v>100</v>
-      </c>
       <c r="AG22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-600</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
       <c r="F23" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3">
         <v>-900</v>
       </c>
       <c r="H23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-1600</v>
       </c>
-      <c r="I23" s="3">
-        <v>100</v>
-      </c>
       <c r="J23" s="3">
+        <v>100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="P23" s="3">
-        <v>-1200</v>
       </c>
       <c r="Q23" s="3">
         <v>-1200</v>
       </c>
       <c r="R23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S23" s="3">
         <v>-1000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-600</v>
-      </c>
-      <c r="V23" s="3">
-        <v>-700</v>
       </c>
       <c r="W23" s="3">
         <v>-700</v>
       </c>
       <c r="X23" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Y23" s="3">
         <v>-500</v>
@@ -2151,31 +2194,34 @@
         <v>-500</v>
       </c>
       <c r="AA23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-300</v>
       </c>
-      <c r="AG23" s="3">
-        <v>0</v>
-      </c>
       <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2206,14 +2252,14 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>4</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>4</v>
@@ -2230,8 +2276,8 @@
       <c r="T24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,73 +2419,76 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
       <c r="F26" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="G26" s="3">
         <v>-900</v>
       </c>
       <c r="H26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-1600</v>
       </c>
-      <c r="I26" s="3">
-        <v>100</v>
-      </c>
       <c r="J26" s="3">
+        <v>100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-12600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="P26" s="3">
-        <v>-1200</v>
       </c>
       <c r="Q26" s="3">
         <v>-1200</v>
       </c>
       <c r="R26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-600</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-700</v>
       </c>
       <c r="W26" s="3">
         <v>-700</v>
       </c>
       <c r="X26" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Y26" s="3">
         <v>-500</v>
@@ -2445,96 +2497,99 @@
         <v>-500</v>
       </c>
       <c r="AA26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-300</v>
       </c>
-      <c r="AG26" s="3">
-        <v>0</v>
-      </c>
       <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-600</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="G27" s="3">
         <v>-900</v>
       </c>
       <c r="H27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I27" s="3">
         <v>-1600</v>
       </c>
-      <c r="I27" s="3">
-        <v>100</v>
-      </c>
       <c r="J27" s="3">
+        <v>100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-12600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="P27" s="3">
-        <v>-1200</v>
       </c>
       <c r="Q27" s="3">
         <v>-1200</v>
       </c>
       <c r="R27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-600</v>
-      </c>
-      <c r="V27" s="3">
-        <v>-700</v>
       </c>
       <c r="W27" s="3">
         <v>-700</v>
       </c>
       <c r="X27" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Y27" s="3">
         <v>-500</v>
@@ -2543,31 +2598,34 @@
         <v>-500</v>
       </c>
       <c r="AA27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-300</v>
       </c>
-      <c r="AG27" s="3">
-        <v>0</v>
-      </c>
       <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,8 +3025,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2967,38 +3037,38 @@
         <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
         <v>100</v>
       </c>
       <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
-        <v>100</v>
-      </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>11200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3009,19 +3079,19 @@
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>1900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X32" s="3">
         <v>0</v>
@@ -3035,94 +3105,97 @@
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-600</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="G33" s="3">
         <v>-900</v>
       </c>
       <c r="H33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I33" s="3">
         <v>-1600</v>
       </c>
-      <c r="I33" s="3">
-        <v>100</v>
-      </c>
       <c r="J33" s="3">
+        <v>100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-12600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="P33" s="3">
-        <v>-1200</v>
       </c>
       <c r="Q33" s="3">
         <v>-1200</v>
       </c>
       <c r="R33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-600</v>
-      </c>
-      <c r="V33" s="3">
-        <v>-700</v>
       </c>
       <c r="W33" s="3">
         <v>-700</v>
       </c>
       <c r="X33" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Y33" s="3">
         <v>-500</v>
@@ -3131,31 +3204,34 @@
         <v>-500</v>
       </c>
       <c r="AA33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-300</v>
       </c>
-      <c r="AG33" s="3">
-        <v>0</v>
-      </c>
       <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,73 +3328,76 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-600</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="G35" s="3">
         <v>-900</v>
       </c>
       <c r="H35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I35" s="3">
         <v>-1600</v>
       </c>
-      <c r="I35" s="3">
-        <v>100</v>
-      </c>
       <c r="J35" s="3">
+        <v>100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-12600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="P35" s="3">
-        <v>-1200</v>
       </c>
       <c r="Q35" s="3">
         <v>-1200</v>
       </c>
       <c r="R35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-600</v>
-      </c>
-      <c r="V35" s="3">
-        <v>-700</v>
       </c>
       <c r="W35" s="3">
         <v>-700</v>
       </c>
       <c r="X35" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Y35" s="3">
         <v>-500</v>
@@ -3327,134 +3406,140 @@
         <v>-500</v>
       </c>
       <c r="AA35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-300</v>
       </c>
-      <c r="AG35" s="3">
-        <v>0</v>
-      </c>
       <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E41" s="3">
         <v>2800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>11400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2100</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>2300</v>
       </c>
       <c r="AB41" s="3">
         <v>2300</v>
       </c>
       <c r="AC41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AD41" s="3">
         <v>700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>500</v>
       </c>
-      <c r="AF41" s="3">
-        <v>0</v>
-      </c>
       <c r="AG41" s="3">
         <v>0</v>
       </c>
       <c r="AH41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3646,8 +3736,8 @@
       <c r="I42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J42" s="3">
-        <v>100</v>
+      <c r="J42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K42" s="3">
         <v>100</v>
@@ -3655,8 +3745,8 @@
       <c r="L42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
+      <c r="M42" s="3">
+        <v>100</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>4</v>
@@ -3670,8 +3760,8 @@
       <c r="Q42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -3721,61 +3811,64 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>200</v>
-      </c>
-      <c r="M43" s="3">
-        <v>300</v>
       </c>
       <c r="N43" s="3">
         <v>300</v>
       </c>
       <c r="O43" s="3">
+        <v>300</v>
+      </c>
+      <c r="P43" s="3">
         <v>3100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>200</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3">
         <v>100</v>
@@ -3784,7 +3877,7 @@
         <v>100</v>
       </c>
       <c r="W43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3798,8 +3891,8 @@
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>4</v>
+      <c r="AB43" s="3">
+        <v>0</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>4</v>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3837,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I44" s="3">
         <v>100</v>
@@ -3855,19 +3951,19 @@
         <v>100</v>
       </c>
       <c r="N44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -3915,15 +4011,18 @@
         <v>0</v>
       </c>
       <c r="AH44" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AI44" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>300</v>
@@ -3935,49 +4034,49 @@
         <v>300</v>
       </c>
       <c r="H45" s="3">
+        <v>300</v>
+      </c>
+      <c r="I45" s="3">
         <v>400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>300</v>
-      </c>
-      <c r="J45" s="3">
-        <v>200</v>
       </c>
       <c r="K45" s="3">
         <v>200</v>
       </c>
       <c r="L45" s="3">
+        <v>200</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
-        <v>100</v>
-      </c>
       <c r="O45" s="3">
         <v>100</v>
       </c>
       <c r="P45" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
-        <v>100</v>
-      </c>
       <c r="S45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
       <c r="U45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>200</v>
@@ -3986,7 +4085,7 @@
         <v>200</v>
       </c>
       <c r="Y45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Z45" s="3">
         <v>0</v>
@@ -4012,109 +4111,115 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI45" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>8200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>9200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2200</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>2400</v>
       </c>
       <c r="AB46" s="3">
         <v>2400</v>
       </c>
       <c r="AC46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD46" s="3">
         <v>700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>600</v>
       </c>
-      <c r="AF46" s="3">
-        <v>0</v>
-      </c>
       <c r="AG46" s="3">
         <v>0</v>
       </c>
       <c r="AH46" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="AI46" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4143,19 +4248,19 @@
         <v>0</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
         <v>11200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10800</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>4</v>
+      <c r="P47" s="3">
+        <v>0</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>4</v>
@@ -4172,8 +4277,8 @@
       <c r="U47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4211,8 +4316,11 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4220,28 +4328,28 @@
         <v>600</v>
       </c>
       <c r="E48" s="3">
+        <v>600</v>
+      </c>
+      <c r="F48" s="3">
         <v>700</v>
-      </c>
-      <c r="F48" s="3">
-        <v>800</v>
       </c>
       <c r="G48" s="3">
         <v>800</v>
       </c>
       <c r="H48" s="3">
+        <v>800</v>
+      </c>
+      <c r="I48" s="3">
         <v>900</v>
-      </c>
-      <c r="I48" s="3">
-        <v>800</v>
       </c>
       <c r="J48" s="3">
         <v>800</v>
       </c>
       <c r="K48" s="3">
+        <v>800</v>
+      </c>
+      <c r="L48" s="3">
         <v>900</v>
-      </c>
-      <c r="L48" s="3">
-        <v>200</v>
       </c>
       <c r="M48" s="3">
         <v>200</v>
@@ -4270,8 +4378,8 @@
       <c r="U48" s="3">
         <v>200</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>4</v>
+      <c r="V48" s="3">
+        <v>200</v>
       </c>
       <c r="W48" s="3" t="s">
         <v>4</v>
@@ -4294,8 +4402,8 @@
       <c r="AC48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD48" s="3">
-        <v>0</v>
+      <c r="AD48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
@@ -4309,37 +4417,40 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E49" s="3">
         <v>12000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>12300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>12400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10600</v>
-      </c>
-      <c r="L49" s="3">
-        <v>500</v>
       </c>
       <c r="M49" s="3">
         <v>500</v>
@@ -4351,13 +4462,13 @@
         <v>500</v>
       </c>
       <c r="P49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Q49" s="3">
         <v>400</v>
       </c>
       <c r="R49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S49" s="3">
         <v>300</v>
@@ -4369,10 +4480,10 @@
         <v>300</v>
       </c>
       <c r="V49" s="3">
+        <v>300</v>
+      </c>
+      <c r="W49" s="3">
         <v>400</v>
-      </c>
-      <c r="W49" s="3">
-        <v>300</v>
       </c>
       <c r="X49" s="3">
         <v>300</v>
@@ -4381,7 +4492,7 @@
         <v>300</v>
       </c>
       <c r="Z49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA49" s="3">
         <v>200</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4617,14 +4737,14 @@
       <c r="F52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G52" s="3">
-        <v>200</v>
+      <c r="G52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="H52" s="3">
         <v>200</v>
       </c>
       <c r="I52" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -4632,8 +4752,8 @@
       <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>4</v>
+      <c r="L52" s="3">
+        <v>100</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>4</v>
@@ -4650,8 +4770,8 @@
       <c r="Q52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,97 +4922,100 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E54" s="3">
         <v>17900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>18800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>10300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>800</v>
-      </c>
-      <c r="AF54" s="3">
-        <v>300</v>
       </c>
       <c r="AG54" s="3">
         <v>300</v>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,43 +5099,44 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>500</v>
-      </c>
-      <c r="N57" s="3">
-        <v>400</v>
       </c>
       <c r="O57" s="3">
         <v>400</v>
@@ -5017,10 +5148,10 @@
         <v>400</v>
       </c>
       <c r="R57" s="3">
+        <v>400</v>
+      </c>
+      <c r="S57" s="3">
         <v>500</v>
-      </c>
-      <c r="S57" s="3">
-        <v>400</v>
       </c>
       <c r="T57" s="3">
         <v>400</v>
@@ -5047,28 +5178,31 @@
         <v>400</v>
       </c>
       <c r="AB57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC57" s="3">
         <v>500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1000</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>900</v>
       </c>
       <c r="AG57" s="3">
         <v>900</v>
       </c>
       <c r="AH57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5079,16 +5213,16 @@
         <v>500</v>
       </c>
       <c r="F58" s="3">
+        <v>500</v>
+      </c>
+      <c r="G58" s="3">
         <v>1000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>500</v>
       </c>
       <c r="J58" s="3">
         <v>500</v>
@@ -5096,8 +5230,8 @@
       <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>4</v>
+      <c r="L58" s="3">
+        <v>500</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>4</v>
@@ -5111,8 +5245,8 @@
       <c r="P58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -5124,25 +5258,25 @@
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB58" s="3">
         <v>100</v>
@@ -5157,16 +5291,19 @@
         <v>100</v>
       </c>
       <c r="AF58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG58" s="3">
         <v>200</v>
       </c>
-      <c r="AG58" s="3">
-        <v>100</v>
-      </c>
       <c r="AH58" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5174,29 +5311,29 @@
         <v>1100</v>
       </c>
       <c r="E59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F59" s="3">
         <v>1300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5209,8 +5346,8 @@
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -5219,16 +5356,16 @@
         <v>0</v>
       </c>
       <c r="T59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V59" s="3">
         <v>300</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="X59" s="3">
         <v>100</v>
@@ -5236,8 +5373,8 @@
       <c r="Y59" s="3">
         <v>100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>4</v>
+      <c r="Z59" s="3">
+        <v>100</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>4</v>
@@ -5245,61 +5382,64 @@
       <c r="AB59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE59" s="3">
         <v>100</v>
       </c>
       <c r="AF59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG59" s="3">
         <v>700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>500</v>
-      </c>
-      <c r="N60" s="3">
-        <v>400</v>
       </c>
       <c r="O60" s="3">
         <v>400</v>
@@ -5311,87 +5451,90 @@
         <v>400</v>
       </c>
       <c r="R60" s="3">
+        <v>400</v>
+      </c>
+      <c r="S60" s="3">
         <v>500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>400</v>
-      </c>
-      <c r="X60" s="3">
-        <v>500</v>
       </c>
       <c r="Y60" s="3">
         <v>500</v>
       </c>
       <c r="Z60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA60" s="3">
         <v>400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1400</v>
-      </c>
-      <c r="J61" s="3">
-        <v>1500</v>
       </c>
       <c r="K61" s="3">
         <v>1500</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5403,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>100</v>
@@ -5418,7 +5561,7 @@
         <v>100</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V61" s="3">
         <v>0</v>
@@ -5459,28 +5602,31 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>600</v>
+      </c>
+      <c r="E62" s="3">
         <v>900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1200</v>
       </c>
       <c r="G62" s="3">
         <v>1200</v>
       </c>
       <c r="H62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I62" s="3">
         <v>1400</v>
-      </c>
-      <c r="I62" s="3">
-        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>400</v>
@@ -5489,16 +5635,16 @@
         <v>400</v>
       </c>
       <c r="L62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="M62" s="3">
         <v>100</v>
       </c>
       <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="O62" s="3">
+        <v>0</v>
       </c>
       <c r="P62" s="3" t="s">
         <v>4</v>
@@ -5515,8 +5661,8 @@
       <c r="T62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U62" s="3">
-        <v>0</v>
+      <c r="U62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V62" s="3">
         <v>0</v>
@@ -5551,14 +5697,17 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-      <c r="AG62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH62" s="3">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>500</v>
-      </c>
-      <c r="N66" s="3">
-        <v>400</v>
       </c>
       <c r="O66" s="3">
         <v>400</v>
       </c>
       <c r="P66" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Q66" s="3">
         <v>500</v>
       </c>
       <c r="R66" s="3">
+        <v>500</v>
+      </c>
+      <c r="S66" s="3">
         <v>600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>400</v>
-      </c>
-      <c r="X66" s="3">
-        <v>500</v>
       </c>
       <c r="Y66" s="3">
         <v>500</v>
       </c>
       <c r="Z66" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA66" s="3">
         <v>400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-82700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-82400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-81800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-81900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-80900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-80000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-78500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-78600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-78000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-65500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-64100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-63100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-70200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-68900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-67700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-66500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-65500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-62900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-61800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-61100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-60400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-59800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-59300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-58200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-57500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-42800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-42500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-41900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-41600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,79 +6952,82 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E76" s="3">
         <v>12400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>20200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>22200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>1100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1600</v>
-      </c>
-      <c r="Z76" s="3">
-        <v>2000</v>
       </c>
       <c r="AA76" s="3">
         <v>2000</v>
@@ -6850,25 +7036,28 @@
         <v>2000</v>
       </c>
       <c r="AC76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AD76" s="3">
         <v>-200</v>
       </c>
-      <c r="AD76" s="3">
-        <v>0</v>
-      </c>
       <c r="AE76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF76" s="3">
         <v>-300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,176 +7154,182 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-600</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="G81" s="3">
         <v>-900</v>
       </c>
       <c r="H81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I81" s="3">
         <v>-1600</v>
       </c>
-      <c r="I81" s="3">
-        <v>100</v>
-      </c>
       <c r="J81" s="3">
+        <v>100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-12600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="P81" s="3">
-        <v>-1200</v>
       </c>
       <c r="Q81" s="3">
         <v>-1200</v>
       </c>
       <c r="R81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-600</v>
-      </c>
-      <c r="V81" s="3">
-        <v>-700</v>
       </c>
       <c r="W81" s="3">
         <v>-700</v>
       </c>
       <c r="X81" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Y81" s="3">
         <v>-500</v>
@@ -7143,31 +7338,34 @@
         <v>-500</v>
       </c>
       <c r="AA81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-300</v>
       </c>
-      <c r="AG81" s="3">
-        <v>0</v>
-      </c>
       <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7229,11 +7428,11 @@
         <v>300</v>
       </c>
       <c r="K83" s="3">
+        <v>300</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -7291,17 +7490,20 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>0</v>
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
-        <v>100</v>
-      </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-400</v>
       </c>
       <c r="Z89" s="3">
         <v>-400</v>
       </c>
       <c r="AA89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AB89" s="3">
         <v>-600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-900</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>-300</v>
       </c>
       <c r="AE89" s="3">
         <v>-300</v>
       </c>
       <c r="AF89" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AG89" s="3">
         <v>-100</v>
       </c>
       <c r="AH89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7936,7 +8157,7 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-200</v>
@@ -7945,25 +8166,25 @@
         <v>-200</v>
       </c>
       <c r="I91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>4</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>4</v>
@@ -7977,14 +8198,14 @@
       <c r="S91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
+      <c r="T91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
@@ -7998,8 +8219,8 @@
       <c r="Z91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -8022,8 +8243,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,8 +8445,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8230,43 +8460,43 @@
         <v>-100</v>
       </c>
       <c r="F94" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="G94" s="3">
         <v>-200</v>
       </c>
       <c r="H94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I94" s="3">
         <v>-600</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-100</v>
       </c>
       <c r="J94" s="3">
         <v>-100</v>
       </c>
       <c r="K94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L94" s="3">
         <v>-7600</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
       <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3000</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-100</v>
       </c>
       <c r="Q94" s="3">
         <v>-100</v>
       </c>
       <c r="R94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S94" s="3">
         <v>0</v>
@@ -8275,23 +8505,23 @@
         <v>0</v>
       </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
@@ -8301,14 +8531,14 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>4</v>
+      <c r="AD94" s="3">
+        <v>0</v>
       </c>
       <c r="AE94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF94" s="3">
-        <v>0</v>
+      <c r="AF94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG94" s="3">
         <v>0</v>
@@ -8316,8 +8546,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,71 +8987,74 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300</v>
       </c>
-      <c r="J100" s="3">
-        <v>100</v>
-      </c>
       <c r="K100" s="3">
+        <v>100</v>
+      </c>
+      <c r="L100" s="3">
         <v>4500</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8400</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
         <v>0</v>
       </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>9100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>500</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
         <v>0</v>
       </c>
@@ -8816,34 +9062,37 @@
         <v>0</v>
       </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>800</v>
       </c>
-      <c r="AF100" s="3">
-        <v>100</v>
-      </c>
       <c r="AG100" s="3">
         <v>100</v>
       </c>
       <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8862,8 +9111,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>4</v>
@@ -8880,8 +9129,8 @@
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
-        <v>100</v>
-      </c>
       <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-400</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-300</v>
       </c>
       <c r="I102" s="3">
         <v>-300</v>
       </c>
       <c r="J102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="K102" s="3">
         <v>-100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>7400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="V102" s="3">
-        <v>100</v>
-      </c>
       <c r="W102" s="3">
+        <v>100</v>
+      </c>
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>1600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>500</v>
       </c>
-      <c r="AF102" s="3">
-        <v>0</v>
-      </c>
       <c r="AG102" s="3">
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>VRME</t>
   </si>
@@ -656,151 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -808,47 +812,47 @@
         <v>5400</v>
       </c>
       <c r="E8" s="3">
+        <v>5400</v>
+      </c>
+      <c r="F8" s="3">
         <v>5800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
-      </c>
-      <c r="N8" s="3">
-        <v>300</v>
       </c>
       <c r="O8" s="3">
         <v>300</v>
       </c>
       <c r="P8" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q8" s="3">
+        <v>100</v>
+      </c>
+      <c r="R8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3">
-        <v>100</v>
-      </c>
       <c r="S8" s="3">
         <v>100</v>
       </c>
@@ -865,7 +869,7 @@
         <v>100</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -879,11 +883,11 @@
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-      <c r="AC8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>0</v>
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE8" s="3">
         <v>0</v>
@@ -900,49 +904,52 @@
       <c r="AI8" s="3">
         <v>0</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E9" s="3">
         <v>3300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5600</v>
       </c>
-      <c r="G9" s="3">
-        <v>3300</v>
-      </c>
       <c r="H9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I9" s="3">
         <v>3700</v>
       </c>
-      <c r="I9" s="3">
-        <v>3900</v>
-      </c>
       <c r="J9" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K9" s="3">
         <v>6900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2800</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
-      </c>
       <c r="N9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O9" s="3">
         <v>100</v>
       </c>
       <c r="P9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="3">
         <v>0</v>
@@ -980,8 +987,8 @@
       <c r="AB9" s="3">
         <v>0</v>
       </c>
-      <c r="AC9" s="3" t="s">
-        <v>4</v>
+      <c r="AC9" s="3">
+        <v>0</v>
       </c>
       <c r="AD9" s="3" t="s">
         <v>4</v>
@@ -995,46 +1002,49 @@
       <c r="AG9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3" t="s">
+      <c r="AH9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3100</v>
       </c>
-      <c r="G10" s="3">
-        <v>2300</v>
-      </c>
       <c r="H10" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I10" s="3">
         <v>1600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K10" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L10" s="3">
         <v>1800</v>
       </c>
-      <c r="J10" s="3">
-        <v>2800</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1800</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1700</v>
-      </c>
-      <c r="M10" s="3">
-        <v>200</v>
       </c>
       <c r="N10" s="3">
         <v>200</v>
@@ -1043,14 +1053,14 @@
         <v>200</v>
       </c>
       <c r="P10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Q10" s="3">
+        <v>100</v>
+      </c>
+      <c r="R10" s="3">
         <v>200</v>
       </c>
-      <c r="R10" s="3">
-        <v>100</v>
-      </c>
       <c r="S10" s="3">
         <v>100</v>
       </c>
@@ -1067,7 +1077,7 @@
         <v>100</v>
       </c>
       <c r="X10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y10" s="3">
         <v>0</v>
@@ -1081,8 +1091,8 @@
       <c r="AB10" s="3">
         <v>0</v>
       </c>
-      <c r="AC10" s="3" t="s">
-        <v>4</v>
+      <c r="AC10" s="3">
+        <v>0</v>
       </c>
       <c r="AD10" s="3" t="s">
         <v>4</v>
@@ -1096,14 +1106,17 @@
       <c r="AG10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="3" t="s">
+      <c r="AH10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1148,13 +1162,13 @@
         <v>0</v>
       </c>
       <c r="E12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12" s="3">
         <v>100</v>
       </c>
       <c r="G12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="3">
         <v>0</v>
@@ -1195,14 +1209,14 @@
       <c r="T12" s="3">
         <v>0</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>4</v>
+      <c r="U12" s="3">
+        <v>0</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W12" s="3">
-        <v>0</v>
+      <c r="W12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X12" s="3">
         <v>0</v>
@@ -1211,22 +1225,22 @@
         <v>0</v>
       </c>
       <c r="Z12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="3">
         <v>100</v>
       </c>
       <c r="AB12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC12" s="3">
         <v>0</v>
       </c>
       <c r="AD12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF12" s="3">
         <v>0</v>
@@ -1237,11 +1251,14 @@
       <c r="AH12" s="3">
         <v>0</v>
       </c>
-      <c r="AI12" s="3" t="s">
+      <c r="AI12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,52 +1358,55 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
+      <c r="D14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-200</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>4</v>
+        <v>200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>300</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-200</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N14" s="3">
-        <v>100</v>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O14" s="3">
         <v>100</v>
       </c>
       <c r="P14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>100</v>
@@ -1398,16 +1418,16 @@
         <v>100</v>
       </c>
       <c r="U14" s="3">
+        <v>100</v>
+      </c>
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
-        <v>100</v>
-      </c>
       <c r="W14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="3">
         <v>100</v>
@@ -1416,57 +1436,60 @@
         <v>100</v>
       </c>
       <c r="AA14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>200</v>
       </c>
-      <c r="AE14" s="3">
-        <v>100</v>
-      </c>
       <c r="AF14" s="3">
         <v>100</v>
       </c>
       <c r="AG14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3">
         <v>100</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>4</v>
+      <c r="D15" s="3">
+        <v>300</v>
+      </c>
+      <c r="E15" s="3">
+        <v>300</v>
+      </c>
+      <c r="F15" s="3">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3">
+        <v>300</v>
+      </c>
+      <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
+        <v>300</v>
+      </c>
+      <c r="J15" s="3">
+        <v>300</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>4</v>
@@ -1474,8 +1497,8 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1489,8 +1512,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>4</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>4</v>
@@ -1507,8 +1530,8 @@
       <c r="W15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,67 +1603,68 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E17" s="3">
         <v>5900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6400</v>
       </c>
-      <c r="F17" s="3">
-        <v>8600</v>
-      </c>
       <c r="G17" s="3">
-        <v>6500</v>
+        <v>8400</v>
       </c>
       <c r="H17" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I17" s="3">
         <v>6400</v>
       </c>
-      <c r="I17" s="3">
-        <v>7200</v>
-      </c>
       <c r="J17" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K17" s="3">
         <v>9600</v>
-      </c>
-      <c r="K17" s="3">
-        <v>5800</v>
       </c>
       <c r="L17" s="3">
         <v>5800</v>
       </c>
       <c r="M17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="N17" s="3">
         <v>1800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
-      </c>
-      <c r="V17" s="3">
-        <v>700</v>
       </c>
       <c r="W17" s="3">
         <v>700</v>
@@ -1646,141 +1673,147 @@
         <v>700</v>
       </c>
       <c r="Y17" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Z17" s="3">
         <v>600</v>
       </c>
       <c r="AA17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB17" s="3">
         <v>500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
-        <v>100</v>
-      </c>
       <c r="G18" s="3">
+        <v>300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="K18" s="3">
+        <v>100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="O18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="R18" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V18" s="3">
         <v>-900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="J18" s="3">
-        <v>100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="M18" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="N18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="R18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="S18" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-700</v>
-      </c>
-      <c r="U18" s="3">
-        <v>-900</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-600</v>
       </c>
       <c r="W18" s="3">
         <v>-600</v>
       </c>
       <c r="X18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-700</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-600</v>
       </c>
       <c r="Z18" s="3">
         <v>-600</v>
       </c>
       <c r="AA18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-800</v>
       </c>
-      <c r="AC18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,177 +1849,181 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G20" s="3">
+        <v>100</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="N20" s="3">
+        <v>200</v>
+      </c>
+      <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
+        <v>8200</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-11200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>8200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>200</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>1200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E21" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
-        <v>300</v>
-      </c>
       <c r="G21" s="3">
+        <v>500</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>400</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="O21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P21" s="3">
+        <v>7200</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="R21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="S21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U21" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="V21" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W21" s="3">
         <v>-600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-12300</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="N21" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="O21" s="3">
-        <v>7200</v>
-      </c>
-      <c r="P21" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="R21" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="S21" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="T21" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="U21" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-600</v>
-      </c>
-      <c r="W21" s="3">
-        <v>-700</v>
       </c>
       <c r="X21" s="3">
         <v>-700</v>
       </c>
       <c r="Y21" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Z21" s="3">
         <v>-500</v>
@@ -1995,31 +2032,34 @@
         <v>-500</v>
       </c>
       <c r="AB21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC21" s="3">
         <v>-800</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-600</v>
       </c>
-      <c r="AG21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH21" s="3">
-        <v>100</v>
+      <c r="AH21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2080,8 +2120,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>4</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>4</v>
@@ -2098,97 +2138,100 @@
       <c r="AB22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
         <v>200</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>200</v>
       </c>
-      <c r="AG22" s="3">
-        <v>100</v>
-      </c>
       <c r="AH22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-600</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
         <v>-900</v>
       </c>
       <c r="I23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1600</v>
       </c>
-      <c r="J23" s="3">
-        <v>100</v>
-      </c>
       <c r="K23" s="3">
+        <v>100</v>
+      </c>
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Q23" s="3">
-        <v>-1200</v>
       </c>
       <c r="R23" s="3">
         <v>-1200</v>
       </c>
       <c r="S23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-600</v>
-      </c>
-      <c r="W23" s="3">
-        <v>-700</v>
       </c>
       <c r="X23" s="3">
         <v>-700</v>
       </c>
       <c r="Y23" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Z23" s="3">
         <v>-500</v>
@@ -2197,31 +2240,34 @@
         <v>-500</v>
       </c>
       <c r="AB23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC23" s="3">
         <v>-800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-300</v>
       </c>
-      <c r="AH23" s="3">
-        <v>0</v>
-      </c>
       <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2255,14 +2301,14 @@
       <c r="M24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
+      <c r="N24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>4</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>4</v>
@@ -2279,8 +2325,8 @@
       <c r="U24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -2321,8 +2367,11 @@
       <c r="AI24" s="3">
         <v>0</v>
       </c>
+      <c r="AJ24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,76 +2471,79 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-600</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="H26" s="3">
         <v>-900</v>
       </c>
       <c r="I26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1600</v>
       </c>
-      <c r="J26" s="3">
-        <v>100</v>
-      </c>
       <c r="K26" s="3">
+        <v>100</v>
+      </c>
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-12600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>-1200</v>
       </c>
       <c r="R26" s="3">
         <v>-1200</v>
       </c>
       <c r="S26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-600</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-700</v>
       </c>
       <c r="X26" s="3">
         <v>-700</v>
       </c>
       <c r="Y26" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Z26" s="3">
         <v>-500</v>
@@ -2500,99 +2552,102 @@
         <v>-500</v>
       </c>
       <c r="AB26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-300</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
       <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3">
         <v>-900</v>
       </c>
       <c r="I27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1600</v>
       </c>
-      <c r="J27" s="3">
-        <v>100</v>
-      </c>
       <c r="K27" s="3">
+        <v>100</v>
+      </c>
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-12600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>-1200</v>
       </c>
       <c r="R27" s="3">
         <v>-1200</v>
       </c>
       <c r="S27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-600</v>
-      </c>
-      <c r="W27" s="3">
-        <v>-700</v>
       </c>
       <c r="X27" s="3">
         <v>-700</v>
       </c>
       <c r="Y27" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Z27" s="3">
         <v>-500</v>
@@ -2601,31 +2656,34 @@
         <v>-500</v>
       </c>
       <c r="AB27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC27" s="3">
         <v>-800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-300</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
       <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,177 +3095,183 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>11200</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="P32" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V32" s="3">
+        <v>200</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
-        <v>100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>11200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-8200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1900</v>
-      </c>
-      <c r="U32" s="3">
-        <v>200</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
-        <v>100</v>
-      </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>300</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="H33" s="3">
         <v>-900</v>
       </c>
       <c r="I33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1600</v>
       </c>
-      <c r="J33" s="3">
-        <v>100</v>
-      </c>
       <c r="K33" s="3">
+        <v>100</v>
+      </c>
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-12600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>-1200</v>
       </c>
       <c r="R33" s="3">
         <v>-1200</v>
       </c>
       <c r="S33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-600</v>
-      </c>
-      <c r="W33" s="3">
-        <v>-700</v>
       </c>
       <c r="X33" s="3">
         <v>-700</v>
       </c>
       <c r="Y33" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Z33" s="3">
         <v>-500</v>
@@ -3207,31 +3280,34 @@
         <v>-500</v>
       </c>
       <c r="AB33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-300</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
       <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,76 +3407,79 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3">
         <v>-900</v>
       </c>
       <c r="I35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1600</v>
       </c>
-      <c r="J35" s="3">
-        <v>100</v>
-      </c>
       <c r="K35" s="3">
+        <v>100</v>
+      </c>
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-12600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>-1200</v>
       </c>
       <c r="R35" s="3">
         <v>-1200</v>
       </c>
       <c r="S35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-600</v>
-      </c>
-      <c r="W35" s="3">
-        <v>-700</v>
       </c>
       <c r="X35" s="3">
         <v>-700</v>
       </c>
       <c r="Y35" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Z35" s="3">
         <v>-500</v>
@@ -3409,137 +3488,143 @@
         <v>-500</v>
       </c>
       <c r="AB35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-300</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
       <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,135 +3698,139 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E41" s="3">
         <v>2900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2100</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>2300</v>
       </c>
       <c r="AC41" s="3">
         <v>2300</v>
       </c>
       <c r="AD41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AE41" s="3">
         <v>700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>500</v>
       </c>
-      <c r="AG41" s="3">
-        <v>0</v>
-      </c>
       <c r="AH41" s="3">
         <v>0</v>
       </c>
       <c r="AI41" s="3">
         <v>0</v>
       </c>
+      <c r="AJ41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K42" s="3">
-        <v>100</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>100</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L42" s="3">
         <v>100</v>
@@ -3748,8 +3838,8 @@
       <c r="M42" s="3">
         <v>100</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>4</v>
+      <c r="N42" s="3">
+        <v>100</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>4</v>
@@ -3763,8 +3853,8 @@
       <c r="R42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="S42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
@@ -3814,8 +3904,11 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3823,55 +3916,55 @@
         <v>2000</v>
       </c>
       <c r="E43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F43" s="3">
         <v>2100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>200</v>
-      </c>
-      <c r="N43" s="3">
-        <v>300</v>
       </c>
       <c r="O43" s="3">
         <v>300</v>
       </c>
       <c r="P43" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q43" s="3">
         <v>3100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>200</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
       <c r="S43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
         <v>100</v>
@@ -3880,7 +3973,7 @@
         <v>100</v>
       </c>
       <c r="X43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3894,8 +3987,8 @@
       <c r="AB43" s="3">
         <v>0</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>4</v>
+      <c r="AC43" s="3">
+        <v>0</v>
       </c>
       <c r="AD43" s="3" t="s">
         <v>4</v>
@@ -3915,8 +4008,11 @@
       <c r="AI43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3936,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="I44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3">
         <v>100</v>
@@ -3954,19 +4050,19 @@
         <v>100</v>
       </c>
       <c r="O44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -4014,72 +4110,75 @@
         <v>0</v>
       </c>
       <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>200</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K45" s="3">
         <v>300</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>200</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
       </c>
       <c r="M45" s="3">
+        <v>200</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
-        <v>100</v>
-      </c>
       <c r="P45" s="3">
         <v>100</v>
       </c>
       <c r="Q45" s="3">
+        <v>100</v>
+      </c>
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
-        <v>100</v>
-      </c>
       <c r="T45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U45" s="3">
         <v>0</v>
       </c>
       <c r="V45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X45" s="3">
         <v>200</v>
@@ -4088,7 +4187,7 @@
         <v>200</v>
       </c>
       <c r="Z45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AA45" s="3">
         <v>0</v>
@@ -4114,135 +4213,141 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-      <c r="AI45" s="3" t="s">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>8200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>9200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2200</v>
-      </c>
-      <c r="AB46" s="3">
-        <v>2400</v>
       </c>
       <c r="AC46" s="3">
         <v>2400</v>
       </c>
       <c r="AD46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AE46" s="3">
         <v>700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>600</v>
       </c>
-      <c r="AG46" s="3">
-        <v>0</v>
-      </c>
       <c r="AH46" s="3">
         <v>0</v>
       </c>
       <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4251,19 +4356,19 @@
         <v>0</v>
       </c>
       <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>11200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10800</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>4</v>
+      <c r="Q47" s="3">
+        <v>0</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>4</v>
@@ -4280,8 +4385,8 @@
       <c r="V47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -4319,40 +4424,43 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E48" s="3">
         <v>600</v>
       </c>
       <c r="F48" s="3">
+        <v>600</v>
+      </c>
+      <c r="G48" s="3">
         <v>700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>800</v>
       </c>
       <c r="H48" s="3">
         <v>800</v>
       </c>
       <c r="I48" s="3">
+        <v>800</v>
+      </c>
+      <c r="J48" s="3">
         <v>900</v>
-      </c>
-      <c r="J48" s="3">
-        <v>800</v>
       </c>
       <c r="K48" s="3">
         <v>800</v>
       </c>
       <c r="L48" s="3">
+        <v>800</v>
+      </c>
+      <c r="M48" s="3">
         <v>900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>200</v>
       </c>
       <c r="N48" s="3">
         <v>200</v>
@@ -4381,8 +4489,8 @@
       <c r="V48" s="3">
         <v>200</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>4</v>
+      <c r="W48" s="3">
+        <v>200</v>
       </c>
       <c r="X48" s="3" t="s">
         <v>4</v>
@@ -4405,8 +4513,8 @@
       <c r="AD48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF48" s="3">
         <v>0</v>
@@ -4420,40 +4528,43 @@
       <c r="AI48" s="3">
         <v>0</v>
       </c>
+      <c r="AJ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F49" s="3">
         <v>11900</v>
       </c>
-      <c r="E49" s="3">
-        <v>12000</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
+        <v>12100</v>
+      </c>
+      <c r="H49" s="3">
+        <v>12200</v>
+      </c>
+      <c r="I49" s="3">
         <v>12300</v>
       </c>
-      <c r="G49" s="3">
-        <v>12400</v>
-      </c>
-      <c r="H49" s="3">
-        <v>12300</v>
-      </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10600</v>
-      </c>
-      <c r="M49" s="3">
-        <v>500</v>
       </c>
       <c r="N49" s="3">
         <v>500</v>
@@ -4465,13 +4576,13 @@
         <v>500</v>
       </c>
       <c r="Q49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="R49" s="3">
         <v>400</v>
       </c>
       <c r="S49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T49" s="3">
         <v>300</v>
@@ -4483,10 +4594,10 @@
         <v>300</v>
       </c>
       <c r="W49" s="3">
+        <v>300</v>
+      </c>
+      <c r="X49" s="3">
         <v>400</v>
-      </c>
-      <c r="X49" s="3">
-        <v>300</v>
       </c>
       <c r="Y49" s="3">
         <v>300</v>
@@ -4495,7 +4606,7 @@
         <v>300</v>
       </c>
       <c r="AA49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AB49" s="3">
         <v>200</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>200</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4740,14 +4860,14 @@
       <c r="G52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H52" s="3">
-        <v>200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>100</v>
+      <c r="H52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K52" s="3">
         <v>100</v>
@@ -4755,8 +4875,8 @@
       <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>4</v>
+      <c r="M52" s="3">
+        <v>100</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>4</v>
@@ -4773,8 +4893,8 @@
       <c r="R52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,100 +5048,103 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E54" s="3">
         <v>17500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>20700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>20800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>18100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>10300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>800</v>
-      </c>
-      <c r="AG54" s="3">
-        <v>300</v>
       </c>
       <c r="AH54" s="3">
         <v>300</v>
@@ -5026,8 +5152,11 @@
       <c r="AI54" s="3">
         <v>300</v>
       </c>
+      <c r="AJ54" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,46 +5230,47 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
-      </c>
-      <c r="O57" s="3">
-        <v>400</v>
       </c>
       <c r="P57" s="3">
         <v>400</v>
@@ -5151,10 +5282,10 @@
         <v>400</v>
       </c>
       <c r="S57" s="3">
+        <v>400</v>
+      </c>
+      <c r="T57" s="3">
         <v>500</v>
-      </c>
-      <c r="T57" s="3">
-        <v>400</v>
       </c>
       <c r="U57" s="3">
         <v>400</v>
@@ -5181,51 +5312,54 @@
         <v>400</v>
       </c>
       <c r="AC57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD57" s="3">
         <v>500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1000</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>900</v>
       </c>
       <c r="AH57" s="3">
         <v>900</v>
       </c>
       <c r="AI57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G58" s="3">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="H58" s="3">
-        <v>1300</v>
+        <v>1200</v>
       </c>
       <c r="I58" s="3">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="J58" s="3">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
@@ -5233,8 +5367,8 @@
       <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>4</v>
+      <c r="M58" s="3">
+        <v>500</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>4</v>
@@ -5248,8 +5382,8 @@
       <c r="Q58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -5261,25 +5395,25 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>200</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
       <c r="AB58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC58" s="3">
         <v>100</v>
@@ -5294,49 +5428,52 @@
         <v>100</v>
       </c>
       <c r="AG58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH58" s="3">
         <v>200</v>
       </c>
-      <c r="AH58" s="3">
-        <v>100</v>
-      </c>
       <c r="AI58" s="3">
         <v>100</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="F59" s="3">
-        <v>1300</v>
+        <v>200</v>
       </c>
       <c r="G59" s="3">
-        <v>1100</v>
+        <v>200</v>
       </c>
       <c r="H59" s="3">
+        <v>200</v>
+      </c>
+      <c r="I59" s="3">
+        <v>100</v>
+      </c>
+      <c r="J59" s="3">
+        <v>200</v>
+      </c>
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="I59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1000</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>700</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5349,8 +5486,8 @@
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
+      <c r="R59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S59" s="3">
         <v>0</v>
@@ -5359,16 +5496,16 @@
         <v>0</v>
       </c>
       <c r="U59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="W59" s="3">
         <v>300</v>
       </c>
       <c r="X59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Y59" s="3">
         <v>100</v>
@@ -5376,8 +5513,8 @@
       <c r="Z59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>4</v>
+      <c r="AA59" s="3">
+        <v>100</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>4</v>
@@ -5385,64 +5522,67 @@
       <c r="AC59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF59" s="3">
         <v>100</v>
       </c>
       <c r="AG59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH59" s="3">
         <v>700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>500</v>
-      </c>
-      <c r="O60" s="3">
-        <v>400</v>
       </c>
       <c r="P60" s="3">
         <v>400</v>
@@ -5454,90 +5594,93 @@
         <v>400</v>
       </c>
       <c r="S60" s="3">
+        <v>400</v>
+      </c>
+      <c r="T60" s="3">
         <v>500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>400</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>500</v>
       </c>
       <c r="Z60" s="3">
         <v>500</v>
       </c>
       <c r="AA60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB60" s="3">
         <v>400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1700</v>
+        <v>1800</v>
       </c>
       <c r="E61" s="3">
         <v>1900</v>
       </c>
       <c r="F61" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G61" s="3">
-        <v>2100</v>
+        <v>2300</v>
       </c>
       <c r="H61" s="3">
-        <v>1100</v>
+        <v>2400</v>
       </c>
       <c r="I61" s="3">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="J61" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K61" s="3">
         <v>1400</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1500</v>
       </c>
       <c r="L61" s="3">
         <v>1500</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N61" s="3">
         <v>0</v>
@@ -5549,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>100</v>
@@ -5564,7 +5707,7 @@
         <v>100</v>
       </c>
       <c r="V61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W61" s="3">
         <v>0</v>
@@ -5605,31 +5748,34 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3">
+        <v>400</v>
+      </c>
+      <c r="F62" s="3">
         <v>600</v>
       </c>
-      <c r="E62" s="3">
-        <v>900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1100</v>
-      </c>
       <c r="G62" s="3">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="H62" s="3">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="I62" s="3">
-        <v>1400</v>
+        <v>800</v>
       </c>
       <c r="J62" s="3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="K62" s="3">
         <v>400</v>
@@ -5638,16 +5784,16 @@
         <v>400</v>
       </c>
       <c r="M62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>100</v>
       </c>
       <c r="O62" s="3">
-        <v>0</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>4</v>
@@ -5664,8 +5810,8 @@
       <c r="U62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
@@ -5700,14 +5846,17 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>8200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>500</v>
-      </c>
-      <c r="O66" s="3">
-        <v>400</v>
       </c>
       <c r="P66" s="3">
         <v>400</v>
       </c>
       <c r="Q66" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="R66" s="3">
         <v>500</v>
       </c>
       <c r="S66" s="3">
+        <v>500</v>
+      </c>
+      <c r="T66" s="3">
         <v>600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>400</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>500</v>
       </c>
       <c r="Z66" s="3">
         <v>500</v>
       </c>
       <c r="AA66" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB66" s="3">
         <v>400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-85200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-82700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-82400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-81800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-81900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-80900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-80000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-78500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-78600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-78000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-65500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-64100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-63100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-70200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-68900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-67700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-66500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-65500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-62900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-61800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-61100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-60400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-59800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-59300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-57500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-42800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-42500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-41900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-41600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,82 +7138,85 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E76" s="3">
         <v>12300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1600</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>2000</v>
       </c>
       <c r="AB76" s="3">
         <v>2000</v>
@@ -7039,25 +7225,28 @@
         <v>2000</v>
       </c>
       <c r="AD76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AE76" s="3">
         <v>-200</v>
       </c>
-      <c r="AE76" s="3">
-        <v>0</v>
-      </c>
       <c r="AF76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="3">
         <v>-300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,182 +7346,188 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="H81" s="3">
         <v>-900</v>
       </c>
       <c r="I81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1600</v>
       </c>
-      <c r="J81" s="3">
-        <v>100</v>
-      </c>
       <c r="K81" s="3">
+        <v>100</v>
+      </c>
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-12600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>-1200</v>
       </c>
       <c r="R81" s="3">
         <v>-1200</v>
       </c>
       <c r="S81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="T81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-600</v>
-      </c>
-      <c r="W81" s="3">
-        <v>-700</v>
       </c>
       <c r="X81" s="3">
         <v>-700</v>
       </c>
       <c r="Y81" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="Z81" s="3">
         <v>-500</v>
@@ -7341,31 +7536,34 @@
         <v>-500</v>
       </c>
       <c r="AB81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-300</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
       <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,41 +7599,42 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>300</v>
       </c>
       <c r="L83" s="3">
+        <v>300</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -7493,17 +7692,20 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-      <c r="AG83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>0</v>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
         <v>400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
-        <v>100</v>
-      </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>-1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-400</v>
       </c>
       <c r="AA89" s="3">
         <v>-400</v>
       </c>
       <c r="AB89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-900</v>
-      </c>
-      <c r="AE89" s="3">
-        <v>-300</v>
       </c>
       <c r="AF89" s="3">
         <v>-300</v>
       </c>
       <c r="AG89" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AH89" s="3">
         <v>-100</v>
       </c>
       <c r="AI89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AJ89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,49 +8365,50 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>4</v>
@@ -8201,14 +8422,14 @@
       <c r="T91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>4</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>4</v>
@@ -8222,8 +8443,8 @@
       <c r="AA91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -8246,8 +8467,11 @@
       <c r="AI91" s="3">
         <v>0</v>
       </c>
+      <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,13 +8675,16 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
@@ -8463,43 +8693,43 @@
         <v>-100</v>
       </c>
       <c r="G94" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="H94" s="3">
         <v>-200</v>
       </c>
       <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-600</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-100</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
       </c>
       <c r="L94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M94" s="3">
         <v>-7600</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
       <c r="N94" s="3">
+        <v>0</v>
+      </c>
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-100</v>
       </c>
       <c r="R94" s="3">
         <v>-100</v>
       </c>
       <c r="S94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -8508,23 +8738,23 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
@@ -8534,14 +8764,14 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-      <c r="AE94" s="3" t="s">
-        <v>4</v>
+      <c r="AE94" s="3">
+        <v>0</v>
       </c>
       <c r="AF94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG94" s="3">
-        <v>0</v>
+      <c r="AG94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
@@ -8549,8 +8779,11 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,74 +9233,77 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300</v>
       </c>
-      <c r="K100" s="3">
-        <v>100</v>
-      </c>
       <c r="L100" s="3">
+        <v>100</v>
+      </c>
+      <c r="M100" s="3">
         <v>4500</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>-300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>8400</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>9100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1000</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>500</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
         <v>0</v>
       </c>
@@ -9065,34 +9311,37 @@
         <v>0</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>800</v>
       </c>
-      <c r="AG100" s="3">
-        <v>100</v>
-      </c>
       <c r="AH100" s="3">
         <v>100</v>
       </c>
       <c r="AI100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9105,14 +9354,14 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>4</v>
@@ -9132,8 +9381,8 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
-        <v>100</v>
-      </c>
       <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-400</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-300</v>
       </c>
       <c r="J102" s="3">
         <v>-300</v>
       </c>
       <c r="K102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
-        <v>100</v>
-      </c>
       <c r="X102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-200</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
-      </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>1600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>500</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
-      </c>
       <c r="AH102" s="3">
         <v>0</v>
       </c>
       <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
   <si>
     <t>VRME</t>
   </si>
@@ -656,206 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5400</v>
+        <v>7700</v>
       </c>
       <c r="E8" s="3">
         <v>5400</v>
       </c>
       <c r="F8" s="3">
+        <v>5400</v>
+      </c>
+      <c r="G8" s="3">
         <v>5800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
-      </c>
-      <c r="O8" s="3">
-        <v>300</v>
       </c>
       <c r="P8" s="3">
         <v>300</v>
       </c>
       <c r="Q8" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="R8" s="3">
+        <v>100</v>
+      </c>
+      <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="S8" s="3">
-        <v>100</v>
-      </c>
       <c r="T8" s="3">
         <v>100</v>
       </c>
@@ -872,7 +875,7 @@
         <v>100</v>
       </c>
       <c r="Y8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
@@ -886,11 +889,11 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-      <c r="AD8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="3">
-        <v>0</v>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF8" s="3">
         <v>0</v>
@@ -907,52 +910,55 @@
       <c r="AJ8" s="3">
         <v>0</v>
       </c>
+      <c r="AK8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E9" s="3">
         <v>3500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3500</v>
       </c>
-      <c r="G9" s="3">
-        <v>5600</v>
-      </c>
       <c r="H9" s="3">
+        <v>5800</v>
+      </c>
+      <c r="I9" s="3">
         <v>3600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2800</v>
       </c>
-      <c r="N9" s="3">
-        <v>0</v>
-      </c>
       <c r="O9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P9" s="3">
         <v>100</v>
       </c>
       <c r="Q9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
         <v>0</v>
@@ -990,8 +996,8 @@
       <c r="AC9" s="3">
         <v>0</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>4</v>
+      <c r="AD9" s="3">
+        <v>0</v>
       </c>
       <c r="AE9" s="3" t="s">
         <v>4</v>
@@ -1005,49 +1011,52 @@
       <c r="AH9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="3" t="s">
+      <c r="AI9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2300</v>
       </c>
-      <c r="G10" s="3">
-        <v>3100</v>
-      </c>
       <c r="H10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="I10" s="3">
         <v>2000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>200</v>
       </c>
       <c r="O10" s="3">
         <v>200</v>
@@ -1056,14 +1065,14 @@
         <v>200</v>
       </c>
       <c r="Q10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="R10" s="3">
+        <v>100</v>
+      </c>
+      <c r="S10" s="3">
         <v>200</v>
       </c>
-      <c r="S10" s="3">
-        <v>100</v>
-      </c>
       <c r="T10" s="3">
         <v>100</v>
       </c>
@@ -1080,7 +1089,7 @@
         <v>100</v>
       </c>
       <c r="Y10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z10" s="3">
         <v>0</v>
@@ -1094,8 +1103,8 @@
       <c r="AC10" s="3">
         <v>0</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>4</v>
+      <c r="AD10" s="3">
+        <v>0</v>
       </c>
       <c r="AE10" s="3" t="s">
         <v>4</v>
@@ -1109,14 +1118,17 @@
       <c r="AH10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="3" t="s">
+      <c r="AI10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1165,13 +1178,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3">
         <v>100</v>
       </c>
       <c r="H12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12" s="3">
         <v>0</v>
@@ -1212,14 +1225,14 @@
       <c r="U12" s="3">
         <v>0</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>4</v>
+      <c r="V12" s="3">
+        <v>0</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X12" s="3">
-        <v>0</v>
+      <c r="X12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y12" s="3">
         <v>0</v>
@@ -1228,22 +1241,22 @@
         <v>0</v>
       </c>
       <c r="AA12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="3">
         <v>100</v>
       </c>
       <c r="AC12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
       </c>
       <c r="AE12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG12" s="3">
         <v>0</v>
@@ -1254,11 +1267,14 @@
       <c r="AI12" s="3">
         <v>0</v>
       </c>
-      <c r="AJ12" s="3" t="s">
+      <c r="AJ12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,112 +1377,118 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>500</v>
+      </c>
+      <c r="E14" s="3">
         <v>1800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>300</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K14" s="3">
+        <v>300</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>100</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>100</v>
+      </c>
+      <c r="T14" s="3">
+        <v>100</v>
+      </c>
+      <c r="U14" s="3">
+        <v>100</v>
+      </c>
+      <c r="V14" s="3">
+        <v>100</v>
+      </c>
+      <c r="W14" s="3">
+        <v>300</v>
+      </c>
+      <c r="X14" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>200</v>
       </c>
-      <c r="H14" s="3">
-        <v>300</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-200</v>
-      </c>
-      <c r="J14" s="3">
-        <v>300</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="AE14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O14" s="3">
-        <v>100</v>
-      </c>
-      <c r="P14" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>100</v>
-      </c>
-      <c r="S14" s="3">
-        <v>100</v>
-      </c>
-      <c r="T14" s="3">
-        <v>100</v>
-      </c>
-      <c r="U14" s="3">
-        <v>100</v>
-      </c>
-      <c r="V14" s="3">
-        <v>300</v>
-      </c>
-      <c r="W14" s="3">
-        <v>100</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AF14" s="3">
         <v>200</v>
       </c>
-      <c r="AD14" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>200</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>100</v>
-      </c>
       <c r="AG14" s="3">
         <v>100</v>
       </c>
       <c r="AH14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ14" s="3">
         <v>100</v>
       </c>
+      <c r="AK14" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1513,8 @@
       <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>4</v>
+      <c r="K15" s="3">
+        <v>300</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>4</v>
@@ -1500,8 +1522,8 @@
       <c r="M15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1515,8 +1537,8 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>4</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>4</v>
@@ -1533,8 +1555,8 @@
       <c r="X15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="Y15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,70 +1629,71 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E17" s="3">
         <v>6100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6400</v>
       </c>
-      <c r="G17" s="3">
-        <v>8400</v>
-      </c>
       <c r="H17" s="3">
+        <v>8600</v>
+      </c>
+      <c r="I17" s="3">
         <v>6200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9600</v>
-      </c>
-      <c r="L17" s="3">
-        <v>5800</v>
       </c>
       <c r="M17" s="3">
         <v>5800</v>
       </c>
       <c r="N17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="O17" s="3">
         <v>1800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1000</v>
-      </c>
-      <c r="W17" s="3">
-        <v>700</v>
       </c>
       <c r="X17" s="3">
         <v>700</v>
@@ -1676,144 +1702,150 @@
         <v>700</v>
       </c>
       <c r="Z17" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AA17" s="3">
         <v>600</v>
       </c>
       <c r="AB17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC17" s="3">
         <v>500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
         <v>-600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
-        <v>300</v>
-      </c>
       <c r="H18" s="3">
+        <v>100</v>
+      </c>
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1200</v>
       </c>
-      <c r="K18" s="3">
-        <v>100</v>
-      </c>
       <c r="L18" s="3">
+        <v>100</v>
+      </c>
+      <c r="M18" s="3">
         <v>-600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-900</v>
-      </c>
-      <c r="W18" s="3">
-        <v>-600</v>
       </c>
       <c r="X18" s="3">
         <v>-600</v>
       </c>
       <c r="Y18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-700</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>-600</v>
       </c>
       <c r="AA18" s="3">
         <v>-600</v>
       </c>
       <c r="AB18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-800</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AE18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,13 +1882,14 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>4</v>
@@ -1864,17 +1897,17 @@
       <c r="F20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
+      <c r="G20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="3">
+        <v>100</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1883,20 +1916,20 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-11200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
-        <v>100</v>
-      </c>
       <c r="P20" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q20" s="3">
         <v>8200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1907,20 +1940,20 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
@@ -1933,100 +1966,103 @@
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>300</v>
+      </c>
+      <c r="E21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
-        <v>500</v>
-      </c>
       <c r="H21" s="3">
+        <v>300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-12300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-600</v>
-      </c>
-      <c r="X21" s="3">
-        <v>-700</v>
       </c>
       <c r="Y21" s="3">
         <v>-700</v>
       </c>
       <c r="Z21" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AA21" s="3">
         <v>-500</v>
@@ -2035,31 +2071,34 @@
         <v>-500</v>
       </c>
       <c r="AC21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-800</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AE21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-600</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI21" s="3">
-        <v>100</v>
+      <c r="AI21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK21" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2123,8 +2162,8 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>4</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>4</v>
@@ -2141,100 +2180,103 @@
       <c r="AC22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="3">
         <v>200</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
-      </c>
       <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
         <v>200</v>
       </c>
-      <c r="AH22" s="3">
-        <v>100</v>
-      </c>
       <c r="AI22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
         <v>-900</v>
       </c>
       <c r="J23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K23" s="3">
         <v>-1600</v>
       </c>
-      <c r="K23" s="3">
-        <v>100</v>
-      </c>
       <c r="L23" s="3">
+        <v>100</v>
+      </c>
+      <c r="M23" s="3">
         <v>-600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-12600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>7200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="R23" s="3">
-        <v>-1200</v>
       </c>
       <c r="S23" s="3">
         <v>-1200</v>
       </c>
       <c r="T23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U23" s="3">
         <v>-1000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-600</v>
-      </c>
-      <c r="X23" s="3">
-        <v>-700</v>
       </c>
       <c r="Y23" s="3">
         <v>-700</v>
       </c>
       <c r="Z23" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AA23" s="3">
         <v>-500</v>
@@ -2243,31 +2285,34 @@
         <v>-500</v>
       </c>
       <c r="AC23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD23" s="3">
         <v>-800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-300</v>
       </c>
-      <c r="AI23" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2304,14 +2349,14 @@
       <c r="N24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>4</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>4</v>
@@ -2328,8 +2373,8 @@
       <c r="V24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -2370,8 +2415,11 @@
       <c r="AJ24" s="3">
         <v>0</v>
       </c>
+      <c r="AK24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,79 +2522,82 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="I26" s="3">
         <v>-900</v>
       </c>
       <c r="J26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-1600</v>
       </c>
-      <c r="K26" s="3">
-        <v>100</v>
-      </c>
       <c r="L26" s="3">
+        <v>100</v>
+      </c>
+      <c r="M26" s="3">
         <v>-600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-12600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-1200</v>
       </c>
       <c r="S26" s="3">
         <v>-1200</v>
       </c>
       <c r="T26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-600</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-700</v>
       </c>
       <c r="Y26" s="3">
         <v>-700</v>
       </c>
       <c r="Z26" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AA26" s="3">
         <v>-500</v>
@@ -2555,102 +2606,105 @@
         <v>-500</v>
       </c>
       <c r="AC26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD26" s="3">
         <v>-800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-300</v>
       </c>
-      <c r="AI26" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3">
         <v>-900</v>
       </c>
       <c r="J27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-1600</v>
       </c>
-      <c r="K27" s="3">
-        <v>100</v>
-      </c>
       <c r="L27" s="3">
+        <v>100</v>
+      </c>
+      <c r="M27" s="3">
         <v>-600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-12600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-1400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="R27" s="3">
-        <v>-1200</v>
       </c>
       <c r="S27" s="3">
         <v>-1200</v>
       </c>
       <c r="T27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-600</v>
-      </c>
-      <c r="X27" s="3">
-        <v>-700</v>
       </c>
       <c r="Y27" s="3">
         <v>-700</v>
       </c>
       <c r="Z27" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AA27" s="3">
         <v>-500</v>
@@ -2659,31 +2713,34 @@
         <v>-500</v>
       </c>
       <c r="AC27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD27" s="3">
         <v>-800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-300</v>
       </c>
-      <c r="AI27" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,13 +3164,16 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>4</v>
@@ -3112,17 +3181,17 @@
       <c r="F32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3131,20 +3200,20 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>11200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3155,19 +3224,19 @@
         <v>0</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>1900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
@@ -3181,100 +3250,103 @@
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="I33" s="3">
         <v>-900</v>
       </c>
       <c r="J33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-1600</v>
       </c>
-      <c r="K33" s="3">
-        <v>100</v>
-      </c>
       <c r="L33" s="3">
+        <v>100</v>
+      </c>
+      <c r="M33" s="3">
         <v>-600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-12600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-1400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="R33" s="3">
-        <v>-1200</v>
       </c>
       <c r="S33" s="3">
         <v>-1200</v>
       </c>
       <c r="T33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U33" s="3">
         <v>-1000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-600</v>
-      </c>
-      <c r="X33" s="3">
-        <v>-700</v>
       </c>
       <c r="Y33" s="3">
         <v>-700</v>
       </c>
       <c r="Z33" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AA33" s="3">
         <v>-500</v>
@@ -3283,31 +3355,34 @@
         <v>-500</v>
       </c>
       <c r="AC33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD33" s="3">
         <v>-800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-300</v>
       </c>
-      <c r="AI33" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,79 +3485,82 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3">
         <v>-900</v>
       </c>
       <c r="J35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-1600</v>
       </c>
-      <c r="K35" s="3">
-        <v>100</v>
-      </c>
       <c r="L35" s="3">
+        <v>100</v>
+      </c>
+      <c r="M35" s="3">
         <v>-600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-12600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-1400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="R35" s="3">
-        <v>-1200</v>
       </c>
       <c r="S35" s="3">
         <v>-1200</v>
       </c>
       <c r="T35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U35" s="3">
         <v>-1000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-600</v>
-      </c>
-      <c r="X35" s="3">
-        <v>-700</v>
       </c>
       <c r="Y35" s="3">
         <v>-700</v>
       </c>
       <c r="Z35" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AA35" s="3">
         <v>-500</v>
@@ -3491,140 +3569,146 @@
         <v>-500</v>
       </c>
       <c r="AC35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD35" s="3">
         <v>-800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-300</v>
       </c>
-      <c r="AI35" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E41" s="3">
         <v>2600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>15400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2100</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>2300</v>
       </c>
       <c r="AD41" s="3">
         <v>2300</v>
       </c>
       <c r="AE41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AF41" s="3">
         <v>700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>500</v>
       </c>
-      <c r="AH41" s="3">
-        <v>0</v>
-      </c>
       <c r="AI41" s="3">
         <v>0</v>
       </c>
       <c r="AJ41" s="3">
         <v>0</v>
       </c>
+      <c r="AK41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3821,19 +3910,19 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L42" s="3">
-        <v>100</v>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M42" s="3">
         <v>100</v>
@@ -3841,8 +3930,8 @@
       <c r="N42" s="3">
         <v>100</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
+      <c r="O42" s="3">
+        <v>100</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>4</v>
@@ -3856,8 +3945,8 @@
       <c r="S42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3907,67 +3996,70 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2000</v>
+        <v>3400</v>
       </c>
       <c r="E43" s="3">
         <v>2000</v>
       </c>
       <c r="F43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G43" s="3">
         <v>2100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>200</v>
-      </c>
-      <c r="O43" s="3">
-        <v>300</v>
       </c>
       <c r="P43" s="3">
         <v>300</v>
       </c>
       <c r="Q43" s="3">
+        <v>300</v>
+      </c>
+      <c r="R43" s="3">
         <v>3100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
       <c r="T43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W43" s="3">
         <v>100</v>
@@ -3976,7 +4068,7 @@
         <v>100</v>
       </c>
       <c r="Y43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -3990,8 +4082,8 @@
       <c r="AC43" s="3">
         <v>0</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>4</v>
+      <c r="AD43" s="3">
+        <v>0</v>
       </c>
       <c r="AE43" s="3" t="s">
         <v>4</v>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AK43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4035,7 +4130,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K44" s="3">
         <v>100</v>
@@ -4053,19 +4148,19 @@
         <v>100</v>
       </c>
       <c r="P44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -4113,10 +4208,13 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK44" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,47 +4239,47 @@
       <c r="J45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
         <v>300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>200</v>
       </c>
       <c r="M45" s="3">
         <v>200</v>
       </c>
       <c r="N45" s="3">
+        <v>200</v>
+      </c>
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3">
-        <v>100</v>
-      </c>
       <c r="Q45" s="3">
         <v>100</v>
       </c>
       <c r="R45" s="3">
+        <v>100</v>
+      </c>
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
-        <v>100</v>
-      </c>
       <c r="U45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V45" s="3">
         <v>0</v>
       </c>
       <c r="W45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y45" s="3">
         <v>200</v>
@@ -4190,7 +4288,7 @@
         <v>200</v>
       </c>
       <c r="AA45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AB45" s="3">
         <v>0</v>
@@ -4216,115 +4314,121 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
-      <c r="AJ45" s="3" t="s">
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E46" s="3">
         <v>4800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>9500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>9100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>15800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>8200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>9200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2200</v>
-      </c>
-      <c r="AC46" s="3">
-        <v>2400</v>
       </c>
       <c r="AD46" s="3">
         <v>2400</v>
       </c>
       <c r="AE46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AF46" s="3">
         <v>700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>600</v>
       </c>
-      <c r="AH46" s="3">
-        <v>0</v>
-      </c>
       <c r="AI46" s="3">
         <v>0</v>
       </c>
       <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4349,8 +4453,8 @@
       <c r="J47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4359,19 +4463,19 @@
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>11200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10800</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>4</v>
+      <c r="R47" s="3">
+        <v>0</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>4</v>
@@ -4388,8 +4492,8 @@
       <c r="W47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -4427,43 +4531,46 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>400</v>
+      </c>
+      <c r="E48" s="3">
         <v>500</v>
-      </c>
-      <c r="E48" s="3">
-        <v>600</v>
       </c>
       <c r="F48" s="3">
         <v>600</v>
       </c>
       <c r="G48" s="3">
+        <v>600</v>
+      </c>
+      <c r="H48" s="3">
         <v>700</v>
-      </c>
-      <c r="H48" s="3">
-        <v>800</v>
       </c>
       <c r="I48" s="3">
         <v>800</v>
       </c>
       <c r="J48" s="3">
+        <v>800</v>
+      </c>
+      <c r="K48" s="3">
         <v>900</v>
-      </c>
-      <c r="K48" s="3">
-        <v>800</v>
       </c>
       <c r="L48" s="3">
         <v>800</v>
       </c>
       <c r="M48" s="3">
+        <v>800</v>
+      </c>
+      <c r="N48" s="3">
         <v>900</v>
-      </c>
-      <c r="N48" s="3">
-        <v>200</v>
       </c>
       <c r="O48" s="3">
         <v>200</v>
@@ -4492,8 +4599,8 @@
       <c r="W48" s="3">
         <v>200</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>4</v>
+      <c r="X48" s="3">
+        <v>200</v>
       </c>
       <c r="Y48" s="3" t="s">
         <v>4</v>
@@ -4516,8 +4623,8 @@
       <c r="AE48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF48" s="3">
-        <v>0</v>
+      <c r="AF48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG48" s="3">
         <v>0</v>
@@ -4531,43 +4638,46 @@
       <c r="AJ48" s="3">
         <v>0</v>
       </c>
+      <c r="AK48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E49" s="3">
         <v>9400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>12100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10600</v>
-      </c>
-      <c r="N49" s="3">
-        <v>500</v>
       </c>
       <c r="O49" s="3">
         <v>500</v>
@@ -4579,13 +4689,13 @@
         <v>500</v>
       </c>
       <c r="R49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="S49" s="3">
         <v>400</v>
       </c>
       <c r="T49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="U49" s="3">
         <v>300</v>
@@ -4597,10 +4707,10 @@
         <v>300</v>
       </c>
       <c r="X49" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y49" s="3">
         <v>400</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>300</v>
       </c>
       <c r="Z49" s="3">
         <v>300</v>
@@ -4609,7 +4719,7 @@
         <v>300</v>
       </c>
       <c r="AB49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AC49" s="3">
         <v>200</v>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3">
         <v>200</v>
       </c>
+      <c r="AK49" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4959,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4869,8 +4988,8 @@
       <c r="J52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K52" s="3">
-        <v>100</v>
+      <c r="K52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>100</v>
@@ -4878,8 +4997,8 @@
       <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
+      <c r="N52" s="3">
+        <v>100</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>4</v>
@@ -4896,8 +5015,8 @@
       <c r="S52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
@@ -4947,8 +5066,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,103 +5173,106 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E54" s="3">
         <v>14800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>800</v>
-      </c>
-      <c r="AH54" s="3">
-        <v>300</v>
       </c>
       <c r="AI54" s="3">
         <v>300</v>
@@ -5155,8 +5280,11 @@
       <c r="AJ54" s="3">
         <v>300</v>
       </c>
+      <c r="AK54" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,49 +5360,50 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
-      </c>
-      <c r="P57" s="3">
-        <v>400</v>
       </c>
       <c r="Q57" s="3">
         <v>400</v>
@@ -5285,10 +5415,10 @@
         <v>400</v>
       </c>
       <c r="T57" s="3">
+        <v>400</v>
+      </c>
+      <c r="U57" s="3">
         <v>500</v>
-      </c>
-      <c r="U57" s="3">
-        <v>400</v>
       </c>
       <c r="V57" s="3">
         <v>400</v>
@@ -5315,33 +5445,36 @@
         <v>400</v>
       </c>
       <c r="AD57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE57" s="3">
         <v>500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1000</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>900</v>
       </c>
       <c r="AI57" s="3">
         <v>900</v>
       </c>
       <c r="AJ57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AK57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
         <v>700</v>
@@ -5353,16 +5486,16 @@
         <v>700</v>
       </c>
       <c r="H58" s="3">
+        <v>700</v>
+      </c>
+      <c r="I58" s="3">
         <v>1200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
-      </c>
-      <c r="K58" s="3">
-        <v>500</v>
       </c>
       <c r="L58" s="3">
         <v>500</v>
@@ -5370,8 +5503,8 @@
       <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>4</v>
+      <c r="N58" s="3">
+        <v>500</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>4</v>
@@ -5385,8 +5518,8 @@
       <c r="R58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -5398,25 +5531,25 @@
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>200</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA58" s="3">
-        <v>0</v>
+      <c r="AA58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
       </c>
       <c r="AC58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD58" s="3">
         <v>100</v>
@@ -5431,27 +5564,30 @@
         <v>100</v>
       </c>
       <c r="AH58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI58" s="3">
         <v>200</v>
       </c>
-      <c r="AI58" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ58" s="3">
         <v>100</v>
       </c>
+      <c r="AK58" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G59" s="3">
         <v>200</v>
@@ -5460,23 +5596,23 @@
         <v>200</v>
       </c>
       <c r="I59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J59" s="3">
+        <v>100</v>
+      </c>
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>700</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5489,8 +5625,8 @@
       <c r="R59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
+      <c r="S59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T59" s="3">
         <v>0</v>
@@ -5499,16 +5635,16 @@
         <v>0</v>
       </c>
       <c r="V59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X59" s="3">
         <v>300</v>
       </c>
       <c r="Y59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Z59" s="3">
         <v>100</v>
@@ -5516,8 +5652,8 @@
       <c r="AA59" s="3">
         <v>100</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>4</v>
+      <c r="AB59" s="3">
+        <v>100</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>4</v>
@@ -5525,67 +5661,70 @@
       <c r="AD59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG59" s="3">
         <v>100</v>
       </c>
       <c r="AH59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI59" s="3">
         <v>700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>500</v>
-      </c>
-      <c r="P60" s="3">
-        <v>400</v>
       </c>
       <c r="Q60" s="3">
         <v>400</v>
@@ -5597,93 +5736,96 @@
         <v>400</v>
       </c>
       <c r="T60" s="3">
+        <v>400</v>
+      </c>
+      <c r="U60" s="3">
         <v>500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>400</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>500</v>
       </c>
       <c r="AA60" s="3">
         <v>500</v>
       </c>
       <c r="AB60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC60" s="3">
         <v>400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E61" s="3">
         <v>1800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1400</v>
-      </c>
-      <c r="L61" s="3">
-        <v>1500</v>
       </c>
       <c r="M61" s="3">
         <v>1500</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -5695,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="R61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S61" s="3">
         <v>100</v>
@@ -5710,7 +5852,7 @@
         <v>100</v>
       </c>
       <c r="W61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X61" s="3">
         <v>0</v>
@@ -5751,22 +5893,25 @@
       <c r="AJ61" s="3">
         <v>0</v>
       </c>
+      <c r="AK61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E62" s="3">
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3">
         <v>400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>800</v>
       </c>
       <c r="H62" s="3">
         <v>800</v>
@@ -5775,10 +5920,10 @@
         <v>800</v>
       </c>
       <c r="J62" s="3">
+        <v>800</v>
+      </c>
+      <c r="K62" s="3">
         <v>1000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>400</v>
       </c>
       <c r="L62" s="3">
         <v>400</v>
@@ -5787,16 +5932,16 @@
         <v>400</v>
       </c>
       <c r="N62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="O62" s="3">
         <v>100</v>
       </c>
       <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
       </c>
       <c r="R62" s="3" t="s">
         <v>4</v>
@@ -5813,8 +5958,8 @@
       <c r="V62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
@@ -5849,14 +5994,17 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-      <c r="AI62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ62" s="3">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E66" s="3">
         <v>4500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>500</v>
-      </c>
-      <c r="P66" s="3">
-        <v>400</v>
       </c>
       <c r="Q66" s="3">
         <v>400</v>
       </c>
       <c r="R66" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="S66" s="3">
         <v>500</v>
       </c>
       <c r="T66" s="3">
+        <v>500</v>
+      </c>
+      <c r="U66" s="3">
         <v>600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>400</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>500</v>
       </c>
       <c r="AA66" s="3">
         <v>500</v>
       </c>
       <c r="AB66" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC66" s="3">
         <v>400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-85200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-82700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-82400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-81800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-81900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-80900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-80000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-78500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-78600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-78000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-65500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-64100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-63100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-70200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-68900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-67700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-66500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-65500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-62900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-61800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-61100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-60400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-59800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-59300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-58200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-57500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-42800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-42500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-41900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-41600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,85 +7323,88 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E76" s="3">
         <v>10300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>20200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>21200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>16000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>9100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1600</v>
-      </c>
-      <c r="AB76" s="3">
-        <v>2000</v>
       </c>
       <c r="AC76" s="3">
         <v>2000</v>
@@ -7228,25 +7413,28 @@
         <v>2000</v>
       </c>
       <c r="AE76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AF76" s="3">
         <v>-200</v>
       </c>
-      <c r="AF76" s="3">
-        <v>0</v>
-      </c>
       <c r="AG76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="3">
         <v>-300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>-1400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,188 +7537,194 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="I81" s="3">
         <v>-900</v>
       </c>
       <c r="J81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-1600</v>
       </c>
-      <c r="K81" s="3">
-        <v>100</v>
-      </c>
       <c r="L81" s="3">
+        <v>100</v>
+      </c>
+      <c r="M81" s="3">
         <v>-600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-12600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-1400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="R81" s="3">
-        <v>-1200</v>
       </c>
       <c r="S81" s="3">
         <v>-1200</v>
       </c>
       <c r="T81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="U81" s="3">
         <v>-1000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-600</v>
-      </c>
-      <c r="X81" s="3">
-        <v>-700</v>
       </c>
       <c r="Y81" s="3">
         <v>-700</v>
       </c>
       <c r="Z81" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AA81" s="3">
         <v>-500</v>
@@ -7539,31 +7733,34 @@
         <v>-500</v>
       </c>
       <c r="AC81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AD81" s="3">
         <v>-800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-300</v>
       </c>
-      <c r="AI81" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,8 +7797,9 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7615,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="G83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I83" s="3">
         <v>0</v>
@@ -7627,17 +7825,17 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>300</v>
       </c>
       <c r="M83" s="3">
+        <v>300</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -7695,17 +7893,20 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>0</v>
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E89" s="3">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3">
         <v>400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
-        <v>100</v>
-      </c>
       <c r="L89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>-1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-600</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-400</v>
       </c>
       <c r="AB89" s="3">
         <v>-400</v>
       </c>
       <c r="AC89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-900</v>
-      </c>
-      <c r="AF89" s="3">
-        <v>-300</v>
       </c>
       <c r="AG89" s="3">
         <v>-300</v>
       </c>
       <c r="AH89" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AI89" s="3">
         <v>-100</v>
       </c>
       <c r="AJ89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AK89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8393,25 +8613,25 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L91" s="3">
         <v>-100</v>
       </c>
       <c r="M91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>4</v>
@@ -8425,14 +8645,14 @@
       <c r="U91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>4</v>
@@ -8446,8 +8666,8 @@
       <c r="AB91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -8470,8 +8690,11 @@
       <c r="AJ91" s="3">
         <v>0</v>
       </c>
+      <c r="AK91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,8 +8904,11 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8687,7 +8916,7 @@
         <v>-200</v>
       </c>
       <c r="E94" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F94" s="3">
         <v>-100</v>
@@ -8696,43 +8925,43 @@
         <v>-100</v>
       </c>
       <c r="H94" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I94" s="3">
         <v>-200</v>
       </c>
       <c r="J94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-600</v>
-      </c>
-      <c r="K94" s="3">
-        <v>-100</v>
       </c>
       <c r="L94" s="3">
         <v>-100</v>
       </c>
       <c r="M94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N94" s="3">
         <v>-7600</v>
       </c>
-      <c r="N94" s="3">
-        <v>0</v>
-      </c>
       <c r="O94" s="3">
+        <v>0</v>
+      </c>
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3000</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-100</v>
       </c>
       <c r="S94" s="3">
         <v>-100</v>
       </c>
       <c r="T94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -8741,23 +8970,23 @@
         <v>0</v>
       </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
@@ -8767,14 +8996,14 @@
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>4</v>
+      <c r="AF94" s="3">
+        <v>0</v>
       </c>
       <c r="AG94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH94" s="3">
-        <v>0</v>
+      <c r="AH94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI94" s="3">
         <v>0</v>
@@ -8782,8 +9011,11 @@
       <c r="AJ94" s="3">
         <v>0</v>
       </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,77 +9478,80 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300</v>
       </c>
-      <c r="L100" s="3">
-        <v>100</v>
-      </c>
       <c r="M100" s="3">
+        <v>100</v>
+      </c>
+      <c r="N100" s="3">
         <v>4500</v>
       </c>
-      <c r="N100" s="3">
-        <v>0</v>
-      </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>8400</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
         <v>0</v>
       </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>9100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1000</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>500</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
         <v>0</v>
       </c>
@@ -9314,34 +9559,37 @@
         <v>0</v>
       </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>800</v>
       </c>
-      <c r="AH100" s="3">
-        <v>100</v>
-      </c>
       <c r="AI100" s="3">
         <v>100</v>
       </c>
       <c r="AJ100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9354,8 +9602,8 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>4</v>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>4</v>
@@ -9384,8 +9632,8 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-300</v>
       </c>
-      <c r="E102" s="3">
-        <v>100</v>
-      </c>
       <c r="F102" s="3">
+        <v>100</v>
+      </c>
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
-        <v>100</v>
-      </c>
       <c r="H102" s="3">
+        <v>100</v>
+      </c>
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-400</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-300</v>
       </c>
       <c r="K102" s="3">
         <v>-300</v>
       </c>
       <c r="L102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
-        <v>100</v>
-      </c>
       <c r="Y102" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-200</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>1600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>500</v>
       </c>
-      <c r="AH102" s="3">
-        <v>0</v>
-      </c>
       <c r="AI102" s="3">
         <v>0</v>
       </c>
       <c r="AJ102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
   <si>
     <t>VRME</t>
   </si>
@@ -656,212 +656,216 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E8" s="3">
         <v>7700</v>
-      </c>
-      <c r="E8" s="3">
-        <v>5400</v>
       </c>
       <c r="F8" s="3">
         <v>5400</v>
       </c>
       <c r="G8" s="3">
+        <v>5400</v>
+      </c>
+      <c r="H8" s="3">
         <v>5800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
-      </c>
-      <c r="P8" s="3">
-        <v>300</v>
       </c>
       <c r="Q8" s="3">
         <v>300</v>
       </c>
       <c r="R8" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="S8" s="3">
+        <v>100</v>
+      </c>
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3">
-        <v>100</v>
-      </c>
       <c r="U8" s="3">
         <v>100</v>
       </c>
@@ -878,7 +882,7 @@
         <v>100</v>
       </c>
       <c r="Z8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -892,11 +896,11 @@
       <c r="AD8" s="3">
         <v>0</v>
       </c>
-      <c r="AE8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>0</v>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG8" s="3">
         <v>0</v>
@@ -913,55 +917,58 @@
       <c r="AK8" s="3">
         <v>0</v>
       </c>
+      <c r="AL8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="3">
         <v>5200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2800</v>
       </c>
-      <c r="O9" s="3">
-        <v>0</v>
-      </c>
       <c r="P9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="3">
         <v>100</v>
       </c>
       <c r="R9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9" s="3">
         <v>0</v>
@@ -999,8 +1006,8 @@
       <c r="AD9" s="3">
         <v>0</v>
       </c>
-      <c r="AE9" s="3" t="s">
-        <v>4</v>
+      <c r="AE9" s="3">
+        <v>0</v>
       </c>
       <c r="AF9" s="3" t="s">
         <v>4</v>
@@ -1014,52 +1021,55 @@
       <c r="AI9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="3" t="s">
+      <c r="AJ9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E10" s="3">
         <v>2400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1700</v>
-      </c>
-      <c r="O10" s="3">
-        <v>200</v>
       </c>
       <c r="P10" s="3">
         <v>200</v>
@@ -1068,14 +1078,14 @@
         <v>200</v>
       </c>
       <c r="R10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="S10" s="3">
+        <v>100</v>
+      </c>
+      <c r="T10" s="3">
         <v>200</v>
       </c>
-      <c r="T10" s="3">
-        <v>100</v>
-      </c>
       <c r="U10" s="3">
         <v>100</v>
       </c>
@@ -1092,7 +1102,7 @@
         <v>100</v>
       </c>
       <c r="Z10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA10" s="3">
         <v>0</v>
@@ -1106,8 +1116,8 @@
       <c r="AD10" s="3">
         <v>0</v>
       </c>
-      <c r="AE10" s="3" t="s">
-        <v>4</v>
+      <c r="AE10" s="3">
+        <v>0</v>
       </c>
       <c r="AF10" s="3" t="s">
         <v>4</v>
@@ -1121,14 +1131,17 @@
       <c r="AI10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="s">
+      <c r="AJ10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1181,13 +1195,13 @@
         <v>0</v>
       </c>
       <c r="G12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H12" s="3">
         <v>100</v>
       </c>
       <c r="I12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3">
         <v>0</v>
@@ -1228,14 +1242,14 @@
       <c r="V12" s="3">
         <v>0</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>4</v>
+      <c r="W12" s="3">
+        <v>0</v>
       </c>
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y12" s="3">
-        <v>0</v>
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z12" s="3">
         <v>0</v>
@@ -1244,22 +1258,22 @@
         <v>0</v>
       </c>
       <c r="AB12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="3">
         <v>100</v>
       </c>
       <c r="AD12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE12" s="3">
         <v>0</v>
       </c>
       <c r="AF12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH12" s="3">
         <v>0</v>
@@ -1270,11 +1284,14 @@
       <c r="AJ12" s="3">
         <v>0</v>
       </c>
-      <c r="AK12" s="3" t="s">
+      <c r="AK12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,58 +1397,61 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="3">
-        <v>100</v>
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q14" s="3">
         <v>100</v>
       </c>
       <c r="R14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T14" s="3">
         <v>100</v>
@@ -1443,16 +1463,16 @@
         <v>100</v>
       </c>
       <c r="W14" s="3">
+        <v>100</v>
+      </c>
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
-        <v>100</v>
-      </c>
       <c r="Y14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>100</v>
@@ -1461,34 +1481,37 @@
         <v>100</v>
       </c>
       <c r="AC14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>200</v>
       </c>
-      <c r="AG14" s="3">
-        <v>100</v>
-      </c>
       <c r="AH14" s="3">
         <v>100</v>
       </c>
       <c r="AI14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AK14" s="3">
         <v>100</v>
       </c>
+      <c r="AL14" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,8 +1539,8 @@
       <c r="K15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>4</v>
+      <c r="L15" s="3">
+        <v>300</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>4</v>
@@ -1525,8 +1548,8 @@
       <c r="N15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1540,8 +1563,8 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>4</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>4</v>
@@ -1558,8 +1581,8 @@
       <c r="Y15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1594,8 +1617,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,73 +1656,74 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E17" s="3">
         <v>7700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>6100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9600</v>
-      </c>
-      <c r="M17" s="3">
-        <v>5800</v>
       </c>
       <c r="N17" s="3">
         <v>5800</v>
       </c>
       <c r="O17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="P17" s="3">
         <v>1800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1000</v>
-      </c>
-      <c r="X17" s="3">
-        <v>700</v>
       </c>
       <c r="Y17" s="3">
         <v>700</v>
@@ -1705,147 +1732,153 @@
         <v>700</v>
       </c>
       <c r="AA17" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AB17" s="3">
         <v>600</v>
       </c>
       <c r="AC17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD17" s="3">
         <v>500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="E18" s="3">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
         <v>-600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-600</v>
       </c>
-      <c r="H18" s="3">
-        <v>100</v>
-      </c>
       <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
         <v>-600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-1000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1200</v>
       </c>
-      <c r="L18" s="3">
-        <v>100</v>
-      </c>
       <c r="M18" s="3">
+        <v>100</v>
+      </c>
+      <c r="N18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-900</v>
-      </c>
-      <c r="X18" s="3">
-        <v>-600</v>
       </c>
       <c r="Y18" s="3">
         <v>-600</v>
       </c>
       <c r="Z18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>-600</v>
       </c>
       <c r="AB18" s="3">
         <v>-600</v>
       </c>
       <c r="AC18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-800</v>
       </c>
-      <c r="AE18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,16 +1916,17 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
@@ -1900,17 +1934,17 @@
       <c r="G20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
+      <c r="H20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="3">
+        <v>100</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1919,20 +1953,20 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-11200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
-        <v>100</v>
-      </c>
       <c r="Q20" s="3">
+        <v>100</v>
+      </c>
+      <c r="R20" s="3">
         <v>8200</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -1943,20 +1977,20 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-1900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
@@ -1969,103 +2003,106 @@
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-      <c r="AE20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF20" s="3">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
       <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AI20" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
         <v>1200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
         <v>300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-1400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>-700</v>
       </c>
       <c r="Z21" s="3">
         <v>-700</v>
       </c>
       <c r="AA21" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AB21" s="3">
         <v>-500</v>
@@ -2074,31 +2111,34 @@
         <v>-500</v>
       </c>
       <c r="AD21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-800</v>
       </c>
-      <c r="AE21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-600</v>
       </c>
-      <c r="AI21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ21" s="3">
-        <v>100</v>
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL21" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2165,8 +2205,8 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>4</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>4</v>
@@ -2183,103 +2223,106 @@
       <c r="AD22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="3">
         <v>200</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
       <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="3">
         <v>200</v>
       </c>
-      <c r="AI22" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
       <c r="I23" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3">
         <v>-900</v>
       </c>
       <c r="K23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L23" s="3">
         <v>-1600</v>
       </c>
-      <c r="L23" s="3">
-        <v>100</v>
-      </c>
       <c r="M23" s="3">
+        <v>100</v>
+      </c>
+      <c r="N23" s="3">
         <v>-600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-12600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="S23" s="3">
-        <v>-1200</v>
       </c>
       <c r="T23" s="3">
         <v>-1200</v>
       </c>
       <c r="U23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="V23" s="3">
         <v>-1000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>-700</v>
       </c>
       <c r="Z23" s="3">
         <v>-700</v>
       </c>
       <c r="AA23" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AB23" s="3">
         <v>-500</v>
@@ -2288,31 +2331,34 @@
         <v>-500</v>
       </c>
       <c r="AD23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ23" s="3">
-        <v>0</v>
-      </c>
       <c r="AK23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2352,14 +2398,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>4</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>4</v>
@@ -2376,8 +2422,8 @@
       <c r="W24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
+      <c r="X24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y24" s="3">
         <v>0</v>
@@ -2418,8 +2464,11 @@
       <c r="AK24" s="3">
         <v>0</v>
       </c>
+      <c r="AL24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,82 +2574,85 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
       <c r="I26" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
         <v>-900</v>
       </c>
       <c r="K26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L26" s="3">
         <v>-1600</v>
       </c>
-      <c r="L26" s="3">
-        <v>100</v>
-      </c>
       <c r="M26" s="3">
+        <v>100</v>
+      </c>
+      <c r="N26" s="3">
         <v>-600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-12600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="S26" s="3">
-        <v>-1200</v>
       </c>
       <c r="T26" s="3">
         <v>-1200</v>
       </c>
       <c r="U26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="V26" s="3">
         <v>-1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-700</v>
       </c>
       <c r="Z26" s="3">
         <v>-700</v>
       </c>
       <c r="AA26" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AB26" s="3">
         <v>-500</v>
@@ -2609,105 +2661,108 @@
         <v>-500</v>
       </c>
       <c r="AD26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE26" s="3">
         <v>-800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ26" s="3">
-        <v>0</v>
-      </c>
       <c r="AK26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
       <c r="I27" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
         <v>-900</v>
       </c>
       <c r="K27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L27" s="3">
         <v>-1600</v>
       </c>
-      <c r="L27" s="3">
-        <v>100</v>
-      </c>
       <c r="M27" s="3">
+        <v>100</v>
+      </c>
+      <c r="N27" s="3">
         <v>-600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-12600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="S27" s="3">
-        <v>-1200</v>
       </c>
       <c r="T27" s="3">
         <v>-1200</v>
       </c>
       <c r="U27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="V27" s="3">
         <v>-1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y27" s="3">
-        <v>-700</v>
       </c>
       <c r="Z27" s="3">
         <v>-700</v>
       </c>
       <c r="AA27" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AB27" s="3">
         <v>-500</v>
@@ -2716,31 +2771,34 @@
         <v>-500</v>
       </c>
       <c r="AD27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE27" s="3">
         <v>-800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ27" s="3">
-        <v>0</v>
-      </c>
       <c r="AK27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,16 +3234,19 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>4</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>4</v>
@@ -3184,17 +3254,17 @@
       <c r="G32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -3203,20 +3273,20 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>11200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8200</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3227,19 +3297,19 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>1900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
@@ -3253,103 +3323,106 @@
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-      <c r="AE32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF32" s="3">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
       <c r="I33" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
         <v>-900</v>
       </c>
       <c r="K33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L33" s="3">
         <v>-1600</v>
       </c>
-      <c r="L33" s="3">
-        <v>100</v>
-      </c>
       <c r="M33" s="3">
+        <v>100</v>
+      </c>
+      <c r="N33" s="3">
         <v>-600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-12600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="S33" s="3">
-        <v>-1200</v>
       </c>
       <c r="T33" s="3">
         <v>-1200</v>
       </c>
       <c r="U33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="V33" s="3">
         <v>-1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>-700</v>
       </c>
       <c r="Z33" s="3">
         <v>-700</v>
       </c>
       <c r="AA33" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AB33" s="3">
         <v>-500</v>
@@ -3358,31 +3431,34 @@
         <v>-500</v>
       </c>
       <c r="AD33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE33" s="3">
         <v>-800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ33" s="3">
-        <v>0</v>
-      </c>
       <c r="AK33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,82 +3564,85 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
       <c r="I35" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
         <v>-900</v>
       </c>
       <c r="K35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L35" s="3">
         <v>-1600</v>
       </c>
-      <c r="L35" s="3">
-        <v>100</v>
-      </c>
       <c r="M35" s="3">
+        <v>100</v>
+      </c>
+      <c r="N35" s="3">
         <v>-600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-12600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="S35" s="3">
-        <v>-1200</v>
       </c>
       <c r="T35" s="3">
         <v>-1200</v>
       </c>
       <c r="U35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="V35" s="3">
         <v>-1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>-700</v>
       </c>
       <c r="Z35" s="3">
         <v>-700</v>
       </c>
       <c r="AA35" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AB35" s="3">
         <v>-500</v>
@@ -3572,143 +3651,149 @@
         <v>-500</v>
       </c>
       <c r="AD35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE35" s="3">
         <v>-800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ35" s="3">
-        <v>0</v>
-      </c>
       <c r="AK35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E41" s="3">
         <v>2800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>15400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2100</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>2300</v>
       </c>
       <c r="AE41" s="3">
         <v>2300</v>
       </c>
       <c r="AF41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AG41" s="3">
         <v>700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>500</v>
       </c>
-      <c r="AI41" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ41" s="3">
         <v>0</v>
       </c>
       <c r="AK41" s="3">
         <v>0</v>
       </c>
+      <c r="AL41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3913,19 +4003,19 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M42" s="3">
-        <v>100</v>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N42" s="3">
         <v>100</v>
@@ -3933,8 +4023,8 @@
       <c r="O42" s="3">
         <v>100</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>4</v>
+      <c r="P42" s="3">
+        <v>100</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>4</v>
@@ -3948,8 +4038,8 @@
       <c r="T42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3999,70 +4089,73 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E43" s="3">
         <v>3400</v>
-      </c>
-      <c r="E43" s="3">
-        <v>2000</v>
       </c>
       <c r="F43" s="3">
         <v>2000</v>
       </c>
       <c r="G43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H43" s="3">
         <v>2100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>200</v>
-      </c>
-      <c r="P43" s="3">
-        <v>300</v>
       </c>
       <c r="Q43" s="3">
         <v>300</v>
       </c>
       <c r="R43" s="3">
+        <v>300</v>
+      </c>
+      <c r="S43" s="3">
         <v>3100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
       <c r="U43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X43" s="3">
         <v>100</v>
@@ -4071,7 +4164,7 @@
         <v>100</v>
       </c>
       <c r="Z43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -4085,8 +4178,8 @@
       <c r="AD43" s="3">
         <v>0</v>
       </c>
-      <c r="AE43" s="3" t="s">
-        <v>4</v>
+      <c r="AE43" s="3">
+        <v>0</v>
       </c>
       <c r="AF43" s="3" t="s">
         <v>4</v>
@@ -4106,8 +4199,11 @@
       <c r="AK43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AL43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4133,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="K44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L44" s="3">
         <v>100</v>
@@ -4151,19 +4247,19 @@
         <v>100</v>
       </c>
       <c r="Q44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -4211,10 +4307,13 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4242,47 +4341,47 @@
       <c r="K45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M45" s="3">
         <v>300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>200</v>
       </c>
       <c r="N45" s="3">
         <v>200</v>
       </c>
       <c r="O45" s="3">
+        <v>200</v>
+      </c>
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
-        <v>100</v>
-      </c>
       <c r="R45" s="3">
         <v>100</v>
       </c>
       <c r="S45" s="3">
+        <v>100</v>
+      </c>
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
-        <v>100</v>
-      </c>
       <c r="V45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W45" s="3">
         <v>0</v>
       </c>
       <c r="X45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y45" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z45" s="3">
         <v>200</v>
@@ -4291,7 +4390,7 @@
         <v>200</v>
       </c>
       <c r="AB45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -4317,118 +4416,124 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
-      <c r="AK45" s="3" t="s">
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>9500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>15800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2200</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>2400</v>
       </c>
       <c r="AE46" s="3">
         <v>2400</v>
       </c>
       <c r="AF46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AG46" s="3">
         <v>700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>600</v>
       </c>
-      <c r="AI46" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
       <c r="AK46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4456,8 +4561,8 @@
       <c r="K47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4466,19 +4571,19 @@
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>11200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10800</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>4</v>
+      <c r="S47" s="3">
+        <v>0</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>4</v>
@@ -4495,8 +4600,8 @@
       <c r="X47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -4534,46 +4639,49 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>200</v>
+      </c>
+      <c r="E48" s="3">
         <v>400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>500</v>
-      </c>
-      <c r="F48" s="3">
-        <v>600</v>
       </c>
       <c r="G48" s="3">
         <v>600</v>
       </c>
       <c r="H48" s="3">
+        <v>600</v>
+      </c>
+      <c r="I48" s="3">
         <v>700</v>
-      </c>
-      <c r="I48" s="3">
-        <v>800</v>
       </c>
       <c r="J48" s="3">
         <v>800</v>
       </c>
       <c r="K48" s="3">
+        <v>800</v>
+      </c>
+      <c r="L48" s="3">
         <v>900</v>
-      </c>
-      <c r="L48" s="3">
-        <v>800</v>
       </c>
       <c r="M48" s="3">
         <v>800</v>
       </c>
       <c r="N48" s="3">
+        <v>800</v>
+      </c>
+      <c r="O48" s="3">
         <v>900</v>
-      </c>
-      <c r="O48" s="3">
-        <v>200</v>
       </c>
       <c r="P48" s="3">
         <v>200</v>
@@ -4602,8 +4710,8 @@
       <c r="X48" s="3">
         <v>200</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>4</v>
+      <c r="Y48" s="3">
+        <v>200</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>4</v>
@@ -4626,8 +4734,8 @@
       <c r="AF48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG48" s="3">
-        <v>0</v>
+      <c r="AG48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH48" s="3">
         <v>0</v>
@@ -4641,8 +4749,11 @@
       <c r="AK48" s="3">
         <v>0</v>
       </c>
+      <c r="AL48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4650,37 +4761,37 @@
         <v>9200</v>
       </c>
       <c r="E49" s="3">
+        <v>9200</v>
+      </c>
+      <c r="F49" s="3">
         <v>9400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>10400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10600</v>
-      </c>
-      <c r="O49" s="3">
-        <v>500</v>
       </c>
       <c r="P49" s="3">
         <v>500</v>
@@ -4692,13 +4803,13 @@
         <v>500</v>
       </c>
       <c r="S49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="T49" s="3">
         <v>400</v>
       </c>
       <c r="U49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="V49" s="3">
         <v>300</v>
@@ -4710,10 +4821,10 @@
         <v>300</v>
       </c>
       <c r="Y49" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z49" s="3">
         <v>400</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>300</v>
       </c>
       <c r="AA49" s="3">
         <v>300</v>
@@ -4722,7 +4833,7 @@
         <v>300</v>
       </c>
       <c r="AC49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD49" s="3">
         <v>200</v>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>200</v>
       </c>
+      <c r="AL49" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4991,8 +5111,8 @@
       <c r="K52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L52" s="3">
-        <v>100</v>
+      <c r="L52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M52" s="3">
         <v>100</v>
@@ -5000,8 +5120,8 @@
       <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>4</v>
+      <c r="O52" s="3">
+        <v>100</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>4</v>
@@ -5018,8 +5138,8 @@
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
@@ -5069,8 +5189,11 @@
       <c r="AK52" s="3">
         <v>0</v>
       </c>
+      <c r="AL52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,106 +5299,109 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E54" s="3">
         <v>16100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>17400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>9800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>800</v>
-      </c>
-      <c r="AI54" s="3">
-        <v>300</v>
       </c>
       <c r="AJ54" s="3">
         <v>300</v>
@@ -5283,8 +5409,11 @@
       <c r="AK54" s="3">
         <v>300</v>
       </c>
+      <c r="AL54" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,52 +5491,53 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>3000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>500</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>400</v>
       </c>
       <c r="R57" s="3">
         <v>400</v>
@@ -5418,10 +5549,10 @@
         <v>400</v>
       </c>
       <c r="U57" s="3">
+        <v>400</v>
+      </c>
+      <c r="V57" s="3">
         <v>500</v>
-      </c>
-      <c r="V57" s="3">
-        <v>400</v>
       </c>
       <c r="W57" s="3">
         <v>400</v>
@@ -5448,36 +5579,39 @@
         <v>400</v>
       </c>
       <c r="AE57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF57" s="3">
         <v>500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1000</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>900</v>
       </c>
       <c r="AJ57" s="3">
         <v>900</v>
       </c>
       <c r="AK57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AL57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
-      </c>
-      <c r="E58" s="3">
-        <v>700</v>
       </c>
       <c r="F58" s="3">
         <v>700</v>
@@ -5489,16 +5623,16 @@
         <v>700</v>
       </c>
       <c r="I58" s="3">
+        <v>700</v>
+      </c>
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
-      </c>
-      <c r="L58" s="3">
-        <v>500</v>
       </c>
       <c r="M58" s="3">
         <v>500</v>
@@ -5506,8 +5640,8 @@
       <c r="N58" s="3">
         <v>500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>4</v>
+      <c r="O58" s="3">
+        <v>500</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>4</v>
@@ -5521,8 +5655,8 @@
       <c r="S58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -5534,25 +5668,25 @@
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>200</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AA58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
+      <c r="AB58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC58" s="3">
         <v>0</v>
       </c>
       <c r="AD58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE58" s="3">
         <v>100</v>
@@ -5567,30 +5701,33 @@
         <v>100</v>
       </c>
       <c r="AI58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>200</v>
       </c>
-      <c r="AJ58" s="3">
-        <v>100</v>
-      </c>
       <c r="AK58" s="3">
         <v>100</v>
       </c>
+      <c r="AL58" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E59" s="3">
-        <v>0</v>
+      <c r="E59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G59" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H59" s="3">
         <v>200</v>
@@ -5599,23 +5736,23 @@
         <v>200</v>
       </c>
       <c r="J59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K59" s="3">
+        <v>100</v>
+      </c>
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5628,8 +5765,8 @@
       <c r="S59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
+      <c r="T59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U59" s="3">
         <v>0</v>
@@ -5638,16 +5775,16 @@
         <v>0</v>
       </c>
       <c r="W59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X59" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Y59" s="3">
         <v>300</v>
       </c>
       <c r="Z59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AA59" s="3">
         <v>100</v>
@@ -5655,8 +5792,8 @@
       <c r="AB59" s="3">
         <v>100</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>4</v>
+      <c r="AC59" s="3">
+        <v>100</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>4</v>
@@ -5664,70 +5801,73 @@
       <c r="AE59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF59" s="3">
-        <v>0</v>
+      <c r="AF59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH59" s="3">
         <v>100</v>
       </c>
       <c r="AI59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ59" s="3">
         <v>700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E60" s="3">
         <v>4200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>500</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>400</v>
       </c>
       <c r="R60" s="3">
         <v>400</v>
@@ -5739,96 +5879,99 @@
         <v>400</v>
       </c>
       <c r="U60" s="3">
+        <v>400</v>
+      </c>
+      <c r="V60" s="3">
         <v>500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>400</v>
-      </c>
-      <c r="AA60" s="3">
-        <v>500</v>
       </c>
       <c r="AB60" s="3">
         <v>500</v>
       </c>
       <c r="AC60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD60" s="3">
         <v>400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1400</v>
-      </c>
-      <c r="M61" s="3">
-        <v>1500</v>
       </c>
       <c r="N61" s="3">
         <v>1500</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -5840,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T61" s="3">
         <v>100</v>
@@ -5855,7 +5998,7 @@
         <v>100</v>
       </c>
       <c r="X61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y61" s="3">
         <v>0</v>
@@ -5896,8 +6039,11 @@
       <c r="AK61" s="3">
         <v>0</v>
       </c>
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5907,14 +6053,14 @@
       <c r="E62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>600</v>
-      </c>
-      <c r="H62" s="3">
-        <v>800</v>
       </c>
       <c r="I62" s="3">
         <v>800</v>
@@ -5923,10 +6069,10 @@
         <v>800</v>
       </c>
       <c r="K62" s="3">
+        <v>800</v>
+      </c>
+      <c r="L62" s="3">
         <v>1000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>400</v>
       </c>
       <c r="M62" s="3">
         <v>400</v>
@@ -5935,16 +6081,16 @@
         <v>400</v>
       </c>
       <c r="O62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="P62" s="3">
         <v>100</v>
       </c>
       <c r="Q62" s="3">
-        <v>0</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>4</v>
@@ -5961,8 +6107,8 @@
       <c r="W62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
@@ -5997,14 +6143,17 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E66" s="3">
         <v>5900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>8200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>500</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>400</v>
       </c>
       <c r="R66" s="3">
         <v>400</v>
       </c>
       <c r="S66" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="T66" s="3">
         <v>500</v>
       </c>
       <c r="U66" s="3">
+        <v>500</v>
+      </c>
+      <c r="V66" s="3">
         <v>600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>400</v>
-      </c>
-      <c r="AA66" s="3">
-        <v>500</v>
       </c>
       <c r="AB66" s="3">
         <v>500</v>
       </c>
       <c r="AC66" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD66" s="3">
         <v>400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-86200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-85700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-85200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-82700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-82400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-81800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-81900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-80900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-80000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-78500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-78600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-78000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-65500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-64100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-63100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-70200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-68900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-67700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-66500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-65500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-62900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-61800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-61100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-59800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-59300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-58200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-57500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-42800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-42500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-41900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-41600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,88 +7509,91 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E76" s="3">
         <v>10200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>20200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>21200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>1100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1600</v>
-      </c>
-      <c r="AC76" s="3">
-        <v>2000</v>
       </c>
       <c r="AD76" s="3">
         <v>2000</v>
@@ -7416,25 +7602,28 @@
         <v>2000</v>
       </c>
       <c r="AF76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AG76" s="3">
         <v>-200</v>
       </c>
-      <c r="AG76" s="3">
-        <v>0</v>
-      </c>
       <c r="AH76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI76" s="3">
         <v>-300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>-1400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,194 +7729,200 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
       <c r="I81" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3">
         <v>-900</v>
       </c>
       <c r="K81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="L81" s="3">
         <v>-1600</v>
       </c>
-      <c r="L81" s="3">
-        <v>100</v>
-      </c>
       <c r="M81" s="3">
+        <v>100</v>
+      </c>
+      <c r="N81" s="3">
         <v>-600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-12600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="S81" s="3">
-        <v>-1200</v>
       </c>
       <c r="T81" s="3">
         <v>-1200</v>
       </c>
       <c r="U81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="V81" s="3">
         <v>-1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-600</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>-700</v>
       </c>
       <c r="Z81" s="3">
         <v>-700</v>
       </c>
       <c r="AA81" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AB81" s="3">
         <v>-500</v>
@@ -7736,31 +7931,34 @@
         <v>-500</v>
       </c>
       <c r="AD81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AE81" s="3">
         <v>-800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ81" s="3">
-        <v>0</v>
-      </c>
       <c r="AK81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,8 +7996,9 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7816,10 +8015,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J83" s="3">
         <v>0</v>
@@ -7828,17 +8027,17 @@
         <v>0</v>
       </c>
       <c r="L83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>300</v>
       </c>
       <c r="N83" s="3">
+        <v>300</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -7896,17 +8095,20 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-      <c r="AI83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>0</v>
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E89" s="3">
         <v>600</v>
       </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
       <c r="F89" s="3">
+        <v>0</v>
+      </c>
+      <c r="G89" s="3">
         <v>400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
-        <v>100</v>
-      </c>
       <c r="M89" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>-1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-600</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>-400</v>
       </c>
       <c r="AC89" s="3">
         <v>-400</v>
       </c>
       <c r="AD89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-900</v>
-      </c>
-      <c r="AG89" s="3">
-        <v>-300</v>
       </c>
       <c r="AH89" s="3">
         <v>-300</v>
       </c>
       <c r="AI89" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AJ89" s="3">
         <v>-100</v>
       </c>
       <c r="AK89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AL89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,13 +8806,14 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -8616,25 +8837,25 @@
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3" t="s">
-        <v>4</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>4</v>
@@ -8648,14 +8869,14 @@
       <c r="V91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>4</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>4</v>
@@ -8669,8 +8890,8 @@
       <c r="AC91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -8693,8 +8914,11 @@
       <c r="AK91" s="3">
         <v>0</v>
       </c>
+      <c r="AL91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,19 +9134,22 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-200</v>
+      <c r="D94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E94" s="3">
         <v>-200</v>
       </c>
       <c r="F94" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="G94" s="3">
         <v>-100</v>
@@ -8928,43 +9158,43 @@
         <v>-100</v>
       </c>
       <c r="I94" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="J94" s="3">
         <v>-200</v>
       </c>
       <c r="K94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L94" s="3">
         <v>-600</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-100</v>
       </c>
       <c r="M94" s="3">
         <v>-100</v>
       </c>
       <c r="N94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O94" s="3">
         <v>-7600</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
-      </c>
       <c r="P94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3000</v>
-      </c>
-      <c r="S94" s="3">
-        <v>-100</v>
       </c>
       <c r="T94" s="3">
         <v>-100</v>
       </c>
       <c r="U94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V94" s="3">
         <v>0</v>
@@ -8973,23 +9203,23 @@
         <v>0</v>
       </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
-      </c>
       <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
       <c r="AD94" s="3">
         <v>0</v>
       </c>
@@ -8999,14 +9229,14 @@
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-      <c r="AG94" s="3" t="s">
-        <v>4</v>
+      <c r="AG94" s="3">
+        <v>0</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI94" s="3">
-        <v>0</v>
+      <c r="AI94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ94" s="3">
         <v>0</v>
@@ -9014,8 +9244,11 @@
       <c r="AK94" s="3">
         <v>0</v>
       </c>
+      <c r="AL94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,8 +9316,8 @@
       <c r="K96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,80 +9724,83 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E100" s="3">
         <v>-200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300</v>
       </c>
-      <c r="M100" s="3">
-        <v>100</v>
-      </c>
       <c r="N100" s="3">
+        <v>100</v>
+      </c>
+      <c r="O100" s="3">
         <v>4500</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8400</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
         <v>0</v>
       </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>9100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1000</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>500</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
@@ -9562,34 +9808,37 @@
         <v>0</v>
       </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>800</v>
       </c>
-      <c r="AI100" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ100" s="3">
         <v>100</v>
       </c>
       <c r="AK100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9605,8 +9854,8 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>4</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>4</v>
@@ -9635,8 +9884,8 @@
       <c r="Q101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -9695,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-300</v>
       </c>
-      <c r="F102" s="3">
-        <v>100</v>
-      </c>
       <c r="G102" s="3">
+        <v>100</v>
+      </c>
+      <c r="H102" s="3">
         <v>-300</v>
       </c>
-      <c r="H102" s="3">
-        <v>100</v>
-      </c>
       <c r="I102" s="3">
+        <v>100</v>
+      </c>
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-400</v>
-      </c>
-      <c r="K102" s="3">
-        <v>-300</v>
       </c>
       <c r="L102" s="3">
         <v>-300</v>
       </c>
       <c r="M102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>7400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
-        <v>100</v>
-      </c>
       <c r="Z102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-200</v>
       </c>
-      <c r="AD102" s="3">
-        <v>0</v>
-      </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
         <v>1600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>500</v>
       </c>
-      <c r="AI102" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ102" s="3">
         <v>0</v>
       </c>
       <c r="AK102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="92">
   <si>
     <t>VRME</t>
   </si>
@@ -656,218 +656,222 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3">
         <v>4500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7700</v>
-      </c>
-      <c r="F8" s="3">
-        <v>5400</v>
       </c>
       <c r="G8" s="3">
         <v>5400</v>
       </c>
       <c r="H8" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I8" s="3">
         <v>5800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>300</v>
       </c>
       <c r="R8" s="3">
         <v>300</v>
       </c>
       <c r="S8" s="3">
+        <v>300</v>
+      </c>
+      <c r="T8" s="3">
         <v>100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>200</v>
-      </c>
-      <c r="U8" s="3">
-        <v>100</v>
       </c>
       <c r="V8" s="3">
         <v>100</v>
@@ -885,7 +889,7 @@
         <v>100</v>
       </c>
       <c r="AA8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
@@ -899,11 +903,11 @@
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>0</v>
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH8" s="3">
         <v>0</v>
@@ -920,58 +924,61 @@
       <c r="AL8" s="3">
         <v>0</v>
       </c>
+      <c r="AM8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3">
         <v>3000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2800</v>
       </c>
-      <c r="P9" s="3">
-        <v>0</v>
-      </c>
       <c r="Q9" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R9" s="3">
         <v>100</v>
       </c>
       <c r="S9" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T9" s="3">
         <v>0</v>
@@ -1009,8 +1016,8 @@
       <c r="AE9" s="3">
         <v>0</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>4</v>
+      <c r="AF9" s="3">
+        <v>0</v>
       </c>
       <c r="AG9" s="3" t="s">
         <v>4</v>
@@ -1024,55 +1031,58 @@
       <c r="AJ9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="3" t="s">
+      <c r="AK9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="3">
         <v>1500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1700</v>
-      </c>
-      <c r="P10" s="3">
-        <v>200</v>
       </c>
       <c r="Q10" s="3">
         <v>200</v>
@@ -1081,13 +1091,13 @@
         <v>200</v>
       </c>
       <c r="S10" s="3">
+        <v>200</v>
+      </c>
+      <c r="T10" s="3">
         <v>100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>100</v>
       </c>
       <c r="V10" s="3">
         <v>100</v>
@@ -1105,7 +1115,7 @@
         <v>100</v>
       </c>
       <c r="AA10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB10" s="3">
         <v>0</v>
@@ -1119,8 +1129,8 @@
       <c r="AE10" s="3">
         <v>0</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>4</v>
+      <c r="AF10" s="3">
+        <v>0</v>
       </c>
       <c r="AG10" s="3" t="s">
         <v>4</v>
@@ -1134,14 +1144,17 @@
       <c r="AJ10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AK10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL10" s="3" t="s">
+      <c r="AK10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,13 +1193,14 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>0</v>
+      <c r="D12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -1198,13 +1212,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12" s="3">
         <v>100</v>
       </c>
       <c r="J12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12" s="3">
         <v>0</v>
@@ -1245,14 +1259,14 @@
       <c r="W12" s="3">
         <v>0</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>4</v>
+      <c r="X12" s="3">
+        <v>0</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z12" s="3">
-        <v>0</v>
+      <c r="Z12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA12" s="3">
         <v>0</v>
@@ -1261,23 +1275,23 @@
         <v>0</v>
       </c>
       <c r="AC12" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="3">
         <v>100</v>
       </c>
       <c r="AE12" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF12" s="3">
         <v>0</v>
       </c>
       <c r="AG12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="3">
         <v>100</v>
       </c>
-      <c r="AH12" s="3">
-        <v>0</v>
-      </c>
       <c r="AI12" s="3">
         <v>0</v>
       </c>
@@ -1287,11 +1301,14 @@
       <c r="AK12" s="3">
         <v>0</v>
       </c>
-      <c r="AL12" s="3" t="s">
+      <c r="AL12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,61 +1417,64 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>100</v>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R14" s="3">
         <v>100</v>
       </c>
       <c r="S14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U14" s="3">
         <v>100</v>
@@ -1466,16 +1486,16 @@
         <v>100</v>
       </c>
       <c r="X14" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="3">
         <v>100</v>
@@ -1484,39 +1504,42 @@
         <v>100</v>
       </c>
       <c r="AD14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>200</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>100</v>
       </c>
       <c r="AI14" s="3">
         <v>100</v>
       </c>
       <c r="AJ14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AL14" s="3">
         <v>100</v>
       </c>
+      <c r="AM14" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>300</v>
@@ -1542,8 +1565,8 @@
       <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>4</v>
+      <c r="M15" s="3">
+        <v>300</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>4</v>
@@ -1551,8 +1574,8 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="P15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1566,8 +1589,8 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>4</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>4</v>
@@ -1584,8 +1607,8 @@
       <c r="Z15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1620,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,76 +1683,77 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3">
         <v>5000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9600</v>
-      </c>
-      <c r="N17" s="3">
-        <v>5800</v>
       </c>
       <c r="O17" s="3">
         <v>5800</v>
       </c>
       <c r="P17" s="3">
+        <v>5800</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>700</v>
       </c>
       <c r="Z17" s="3">
         <v>700</v>
@@ -1735,150 +1762,156 @@
         <v>700</v>
       </c>
       <c r="AB17" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AC17" s="3">
         <v>600</v>
       </c>
       <c r="AD17" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE17" s="3">
         <v>500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3">
         <v>-600</v>
       </c>
-      <c r="E18" s="3">
-        <v>0</v>
-      </c>
       <c r="F18" s="3">
+        <v>0</v>
+      </c>
+      <c r="G18" s="3">
         <v>-600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-600</v>
       </c>
       <c r="Z18" s="3">
         <v>-600</v>
       </c>
       <c r="AA18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-600</v>
       </c>
       <c r="AC18" s="3">
         <v>-600</v>
       </c>
       <c r="AD18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-800</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AG18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,19 +1950,20 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>4</v>
@@ -1937,17 +1971,17 @@
       <c r="H20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1956,20 +1990,20 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-11200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8200</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1980,20 +2014,20 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
@@ -2006,106 +2040,109 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
-        <v>0</v>
-      </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3">
         <v>200</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
       <c r="AK20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="3">
         <v>1200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>-300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>7200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>-700</v>
       </c>
       <c r="AA21" s="3">
         <v>-700</v>
       </c>
       <c r="AB21" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AC21" s="3">
         <v>-500</v>
@@ -2114,39 +2151,42 @@
         <v>-500</v>
       </c>
       <c r="AE21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF21" s="3">
         <v>-800</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AK21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL21" s="3">
         <v>100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F22" s="3">
         <v>0</v>
@@ -2208,8 +2248,8 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>4</v>
+      <c r="Z22" s="3">
+        <v>0</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>4</v>
@@ -2226,106 +2266,109 @@
       <c r="AE22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AF22" s="3">
-        <v>0</v>
+      <c r="AF22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
         <v>200</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
       <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>100</v>
       </c>
-      <c r="AK22" s="3">
-        <v>0</v>
-      </c>
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3">
         <v>-600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-2400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-600</v>
       </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
       <c r="J23" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3">
         <v>-900</v>
       </c>
       <c r="L23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M23" s="3">
         <v>-1600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-12600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1400</v>
-      </c>
-      <c r="T23" s="3">
-        <v>-1200</v>
       </c>
       <c r="U23" s="3">
         <v>-1200</v>
       </c>
       <c r="V23" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W23" s="3">
         <v>-1000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z23" s="3">
-        <v>-700</v>
       </c>
       <c r="AA23" s="3">
         <v>-700</v>
       </c>
       <c r="AB23" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AC23" s="3">
         <v>-500</v>
@@ -2334,31 +2377,34 @@
         <v>-500</v>
       </c>
       <c r="AE23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF23" s="3">
         <v>-800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-300</v>
       </c>
-      <c r="AK23" s="3">
-        <v>0</v>
-      </c>
       <c r="AL23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2401,14 +2447,14 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>4</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>4</v>
@@ -2425,8 +2471,8 @@
       <c r="X24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2467,8 +2513,11 @@
       <c r="AL24" s="3">
         <v>0</v>
       </c>
+      <c r="AM24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,85 +2626,88 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="3">
         <v>-600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-2400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-600</v>
       </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
       <c r="J26" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3">
         <v>-900</v>
       </c>
       <c r="L26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M26" s="3">
         <v>-1600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-12600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
-      </c>
-      <c r="T26" s="3">
-        <v>-1200</v>
       </c>
       <c r="U26" s="3">
         <v>-1200</v>
       </c>
       <c r="V26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W26" s="3">
         <v>-1000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-700</v>
       </c>
       <c r="AA26" s="3">
         <v>-700</v>
       </c>
       <c r="AB26" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AC26" s="3">
         <v>-500</v>
@@ -2664,108 +2716,111 @@
         <v>-500</v>
       </c>
       <c r="AE26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF26" s="3">
         <v>-800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-300</v>
       </c>
-      <c r="AK26" s="3">
-        <v>0</v>
-      </c>
       <c r="AL26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3">
         <v>-600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-600</v>
       </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
       <c r="J27" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="K27" s="3">
         <v>-900</v>
       </c>
       <c r="L27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-12600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1400</v>
-      </c>
-      <c r="T27" s="3">
-        <v>-1200</v>
       </c>
       <c r="U27" s="3">
         <v>-1200</v>
       </c>
       <c r="V27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W27" s="3">
         <v>-1000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>-700</v>
       </c>
       <c r="AA27" s="3">
         <v>-700</v>
       </c>
       <c r="AB27" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AC27" s="3">
         <v>-500</v>
@@ -2774,31 +2829,34 @@
         <v>-500</v>
       </c>
       <c r="AE27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF27" s="3">
         <v>-800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-300</v>
       </c>
-      <c r="AK27" s="3">
-        <v>0</v>
-      </c>
       <c r="AL27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,19 +3304,22 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+      <c r="E32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>4</v>
@@ -3257,17 +3327,17 @@
       <c r="H32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3276,20 +3346,20 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>11200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8200</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3300,20 +3370,20 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
@@ -3326,106 +3396,109 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="3">
         <v>-600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-600</v>
       </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
       <c r="J33" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="K33" s="3">
         <v>-900</v>
       </c>
       <c r="L33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-12600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
-      </c>
-      <c r="T33" s="3">
-        <v>-1200</v>
       </c>
       <c r="U33" s="3">
         <v>-1200</v>
       </c>
       <c r="V33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W33" s="3">
         <v>-1000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z33" s="3">
-        <v>-700</v>
       </c>
       <c r="AA33" s="3">
         <v>-700</v>
       </c>
       <c r="AB33" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AC33" s="3">
         <v>-500</v>
@@ -3434,31 +3507,34 @@
         <v>-500</v>
       </c>
       <c r="AE33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF33" s="3">
         <v>-800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-300</v>
       </c>
-      <c r="AK33" s="3">
-        <v>0</v>
-      </c>
       <c r="AL33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,85 +3643,88 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="3">
         <v>-600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-600</v>
       </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
       <c r="J35" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="K35" s="3">
         <v>-900</v>
       </c>
       <c r="L35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-12600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
-      </c>
-      <c r="T35" s="3">
-        <v>-1200</v>
       </c>
       <c r="U35" s="3">
         <v>-1200</v>
       </c>
       <c r="V35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W35" s="3">
         <v>-1000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>-700</v>
       </c>
       <c r="AA35" s="3">
         <v>-700</v>
       </c>
       <c r="AB35" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AC35" s="3">
         <v>-500</v>
@@ -3654,146 +3733,152 @@
         <v>-500</v>
       </c>
       <c r="AE35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF35" s="3">
         <v>-800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-300</v>
       </c>
-      <c r="AK35" s="3">
-        <v>0</v>
-      </c>
       <c r="AL35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="3">
         <v>5700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2100</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>2300</v>
       </c>
       <c r="AF41" s="3">
         <v>2300</v>
       </c>
       <c r="AG41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="AH41" s="3">
         <v>700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>500</v>
       </c>
-      <c r="AJ41" s="3">
-        <v>0</v>
-      </c>
       <c r="AK41" s="3">
         <v>0</v>
       </c>
       <c r="AL41" s="3">
         <v>0</v>
       </c>
+      <c r="AM41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4006,19 +4096,19 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>100</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N42" s="3">
-        <v>100</v>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O42" s="3">
         <v>100</v>
@@ -4026,8 +4116,8 @@
       <c r="P42" s="3">
         <v>100</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>4</v>
+      <c r="Q42" s="3">
+        <v>100</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>4</v>
@@ -4041,8 +4131,8 @@
       <c r="U42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -4092,73 +4182,76 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="3">
         <v>1600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3400</v>
-      </c>
-      <c r="F43" s="3">
-        <v>2000</v>
       </c>
       <c r="G43" s="3">
         <v>2000</v>
       </c>
       <c r="H43" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I43" s="3">
         <v>2100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>200</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>300</v>
       </c>
       <c r="R43" s="3">
         <v>300</v>
       </c>
       <c r="S43" s="3">
+        <v>300</v>
+      </c>
+      <c r="T43" s="3">
         <v>3100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>200</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
       <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
       <c r="X43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="3">
         <v>100</v>
@@ -4167,7 +4260,7 @@
         <v>100</v>
       </c>
       <c r="AA43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB43" s="3">
         <v>0</v>
@@ -4181,8 +4274,8 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>4</v>
+      <c r="AF43" s="3">
+        <v>0</v>
       </c>
       <c r="AG43" s="3" t="s">
         <v>4</v>
@@ -4202,13 +4295,16 @@
       <c r="AL43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AM43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E44" s="3">
         <v>0</v>
@@ -4232,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M44" s="3">
         <v>100</v>
@@ -4250,20 +4346,20 @@
         <v>100</v>
       </c>
       <c r="R44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S44" s="3">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
-      </c>
       <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
         <v>100</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
-      </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
@@ -4310,10 +4406,13 @@
         <v>0</v>
       </c>
       <c r="AL44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,47 +4443,47 @@
       <c r="L45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N45" s="3">
         <v>300</v>
-      </c>
-      <c r="N45" s="3">
-        <v>200</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
       </c>
       <c r="P45" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>100</v>
       </c>
       <c r="S45" s="3">
         <v>100</v>
       </c>
       <c r="T45" s="3">
+        <v>100</v>
+      </c>
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
       <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>100</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>200</v>
       </c>
       <c r="AA45" s="3">
         <v>200</v>
@@ -4393,7 +4492,7 @@
         <v>200</v>
       </c>
       <c r="AC45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -4419,121 +4518,127 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
-      <c r="AL45" s="3" t="s">
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E46" s="3">
         <v>7700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>9500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>9100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>10000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>11100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>8200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2200</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>2400</v>
       </c>
       <c r="AF46" s="3">
         <v>2400</v>
       </c>
       <c r="AG46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AH46" s="3">
         <v>700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>600</v>
       </c>
-      <c r="AJ46" s="3">
-        <v>0</v>
-      </c>
       <c r="AK46" s="3">
         <v>0</v>
       </c>
       <c r="AL46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4564,8 +4669,8 @@
       <c r="L47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4574,19 +4679,19 @@
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>11200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10800</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>4</v>
+      <c r="T47" s="3">
+        <v>0</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>4</v>
@@ -4603,8 +4708,8 @@
       <c r="Y47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4642,49 +4747,52 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>500</v>
-      </c>
-      <c r="G48" s="3">
-        <v>600</v>
       </c>
       <c r="H48" s="3">
         <v>600</v>
       </c>
       <c r="I48" s="3">
+        <v>600</v>
+      </c>
+      <c r="J48" s="3">
         <v>700</v>
-      </c>
-      <c r="J48" s="3">
-        <v>800</v>
       </c>
       <c r="K48" s="3">
         <v>800</v>
       </c>
       <c r="L48" s="3">
+        <v>800</v>
+      </c>
+      <c r="M48" s="3">
         <v>900</v>
-      </c>
-      <c r="M48" s="3">
-        <v>800</v>
       </c>
       <c r="N48" s="3">
         <v>800</v>
       </c>
       <c r="O48" s="3">
+        <v>800</v>
+      </c>
+      <c r="P48" s="3">
         <v>900</v>
-      </c>
-      <c r="P48" s="3">
-        <v>200</v>
       </c>
       <c r="Q48" s="3">
         <v>200</v>
@@ -4713,8 +4821,8 @@
       <c r="Y48" s="3">
         <v>200</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>4</v>
+      <c r="Z48" s="3">
+        <v>200</v>
       </c>
       <c r="AA48" s="3" t="s">
         <v>4</v>
@@ -4737,8 +4845,8 @@
       <c r="AG48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH48" s="3">
-        <v>0</v>
+      <c r="AH48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI48" s="3">
         <v>0</v>
@@ -4752,49 +4860,52 @@
       <c r="AL48" s="3">
         <v>0</v>
       </c>
+      <c r="AM48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E49" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F49" s="3">
         <v>9200</v>
       </c>
-      <c r="E49" s="3">
-        <v>9200</v>
-      </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>9400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>11900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>12200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>12300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10600</v>
-      </c>
-      <c r="P49" s="3">
-        <v>500</v>
       </c>
       <c r="Q49" s="3">
         <v>500</v>
@@ -4806,13 +4917,13 @@
         <v>500</v>
       </c>
       <c r="T49" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="U49" s="3">
         <v>400</v>
       </c>
       <c r="V49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="W49" s="3">
         <v>300</v>
@@ -4824,10 +4935,10 @@
         <v>300</v>
       </c>
       <c r="Z49" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA49" s="3">
         <v>400</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>300</v>
       </c>
       <c r="AB49" s="3">
         <v>300</v>
@@ -4836,7 +4947,7 @@
         <v>300</v>
       </c>
       <c r="AD49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE49" s="3">
         <v>200</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3">
         <v>200</v>
       </c>
+      <c r="AM49" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,8 +5199,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5114,8 +5234,8 @@
       <c r="L52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M52" s="3">
-        <v>100</v>
+      <c r="M52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N52" s="3">
         <v>100</v>
@@ -5123,8 +5243,8 @@
       <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>4</v>
+      <c r="P52" s="3">
+        <v>100</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>4</v>
@@ -5141,8 +5261,8 @@
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
@@ -5192,8 +5312,11 @@
       <c r="AL52" s="3">
         <v>0</v>
       </c>
+      <c r="AM52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,109 +5425,112 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E54" s="3">
         <v>17100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>17500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>20700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>18400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>22600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>9800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>800</v>
-      </c>
-      <c r="AJ54" s="3">
-        <v>300</v>
       </c>
       <c r="AK54" s="3">
         <v>300</v>
@@ -5412,8 +5538,11 @@
       <c r="AL54" s="3">
         <v>300</v>
       </c>
+      <c r="AM54" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,55 +5622,56 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>500</v>
-      </c>
-      <c r="R57" s="3">
-        <v>400</v>
       </c>
       <c r="S57" s="3">
         <v>400</v>
@@ -5552,10 +5683,10 @@
         <v>400</v>
       </c>
       <c r="V57" s="3">
+        <v>400</v>
+      </c>
+      <c r="W57" s="3">
         <v>500</v>
-      </c>
-      <c r="W57" s="3">
-        <v>400</v>
       </c>
       <c r="X57" s="3">
         <v>400</v>
@@ -5582,39 +5713,42 @@
         <v>400</v>
       </c>
       <c r="AF57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG57" s="3">
         <v>500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1000</v>
-      </c>
-      <c r="AJ57" s="3">
-        <v>900</v>
       </c>
       <c r="AK57" s="3">
         <v>900</v>
       </c>
       <c r="AL57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AM57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>600</v>
-      </c>
-      <c r="F58" s="3">
-        <v>700</v>
       </c>
       <c r="G58" s="3">
         <v>700</v>
@@ -5626,16 +5760,16 @@
         <v>700</v>
       </c>
       <c r="J58" s="3">
+        <v>700</v>
+      </c>
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
-      </c>
-      <c r="M58" s="3">
-        <v>500</v>
       </c>
       <c r="N58" s="3">
         <v>500</v>
@@ -5643,8 +5777,8 @@
       <c r="O58" s="3">
         <v>500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>4</v>
+      <c r="P58" s="3">
+        <v>500</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>4</v>
@@ -5658,8 +5792,8 @@
       <c r="T58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -5671,25 +5805,25 @@
         <v>0</v>
       </c>
       <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>200</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC58" s="3">
-        <v>0</v>
+      <c r="AC58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
       </c>
       <c r="AE58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF58" s="3">
         <v>100</v>
@@ -5704,16 +5838,19 @@
         <v>100</v>
       </c>
       <c r="AJ58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK58" s="3">
         <v>200</v>
-      </c>
-      <c r="AK58" s="3">
-        <v>100</v>
       </c>
       <c r="AL58" s="3">
         <v>100</v>
       </c>
+      <c r="AM58" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5723,14 +5860,14 @@
       <c r="E59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F59" s="3">
-        <v>0</v>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>100</v>
-      </c>
-      <c r="H59" s="3">
-        <v>200</v>
       </c>
       <c r="I59" s="3">
         <v>200</v>
@@ -5739,23 +5876,23 @@
         <v>200</v>
       </c>
       <c r="K59" s="3">
+        <v>200</v>
+      </c>
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>4</v>
       </c>
@@ -5768,8 +5905,8 @@
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
+      <c r="U59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
@@ -5778,16 +5915,16 @@
         <v>0</v>
       </c>
       <c r="X59" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="3">
         <v>100</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>300</v>
       </c>
       <c r="Z59" s="3">
         <v>300</v>
       </c>
       <c r="AA59" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AB59" s="3">
         <v>100</v>
@@ -5795,8 +5932,8 @@
       <c r="AC59" s="3">
         <v>100</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>4</v>
+      <c r="AD59" s="3">
+        <v>100</v>
       </c>
       <c r="AE59" s="3" t="s">
         <v>4</v>
@@ -5804,73 +5941,76 @@
       <c r="AF59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG59" s="3">
-        <v>0</v>
+      <c r="AG59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AH59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI59" s="3">
         <v>100</v>
       </c>
       <c r="AJ59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK59" s="3">
         <v>700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E60" s="3">
         <v>1600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>500</v>
-      </c>
-      <c r="R60" s="3">
-        <v>400</v>
       </c>
       <c r="S60" s="3">
         <v>400</v>
@@ -5882,99 +6022,102 @@
         <v>400</v>
       </c>
       <c r="V60" s="3">
+        <v>400</v>
+      </c>
+      <c r="W60" s="3">
         <v>500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>400</v>
-      </c>
-      <c r="AB60" s="3">
-        <v>500</v>
       </c>
       <c r="AC60" s="3">
         <v>500</v>
       </c>
       <c r="AD60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE60" s="3">
         <v>400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>1700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1400</v>
-      </c>
-      <c r="N61" s="3">
-        <v>1500</v>
       </c>
       <c r="O61" s="3">
         <v>1500</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="Q61" s="3">
         <v>0</v>
@@ -5986,7 +6129,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U61" s="3">
         <v>100</v>
@@ -6001,7 +6144,7 @@
         <v>100</v>
       </c>
       <c r="Y61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z61" s="3">
         <v>0</v>
@@ -6042,8 +6185,11 @@
       <c r="AL61" s="3">
         <v>0</v>
       </c>
+      <c r="AM61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6056,14 +6202,14 @@
       <c r="F62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" s="3">
         <v>400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>600</v>
-      </c>
-      <c r="I62" s="3">
-        <v>800</v>
       </c>
       <c r="J62" s="3">
         <v>800</v>
@@ -6072,10 +6218,10 @@
         <v>800</v>
       </c>
       <c r="L62" s="3">
+        <v>800</v>
+      </c>
+      <c r="M62" s="3">
         <v>1000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>400</v>
       </c>
       <c r="N62" s="3">
         <v>400</v>
@@ -6084,16 +6230,16 @@
         <v>400</v>
       </c>
       <c r="P62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="Q62" s="3">
         <v>100</v>
       </c>
       <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>4</v>
@@ -6110,8 +6256,8 @@
       <c r="X62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
@@ -6146,14 +6292,17 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL62" s="3">
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E66" s="3">
         <v>2500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>500</v>
-      </c>
-      <c r="R66" s="3">
-        <v>400</v>
       </c>
       <c r="S66" s="3">
         <v>400</v>
       </c>
       <c r="T66" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="U66" s="3">
         <v>500</v>
       </c>
       <c r="V66" s="3">
+        <v>500</v>
+      </c>
+      <c r="W66" s="3">
         <v>600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>400</v>
-      </c>
-      <c r="AB66" s="3">
-        <v>500</v>
       </c>
       <c r="AC66" s="3">
         <v>500</v>
       </c>
       <c r="AD66" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE66" s="3">
         <v>400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" s="3">
         <v>-86200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-85700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-85200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-82700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-82400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-81800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-81900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-80900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-80000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-78500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-78600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-78000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-65500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-64100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-63100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-70200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-68900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-67700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-66500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-65500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-62900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-61800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-61100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-59800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-59300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-58200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-57500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-42800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-42500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-41900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-41600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,91 +7695,94 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E76" s="3">
         <v>14600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>20200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>21200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>22200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>9800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>1100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>1600</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>2000</v>
       </c>
       <c r="AE76" s="3">
         <v>2000</v>
@@ -7605,25 +7791,28 @@
         <v>2000</v>
       </c>
       <c r="AG76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AH76" s="3">
         <v>-200</v>
       </c>
-      <c r="AH76" s="3">
-        <v>0</v>
-      </c>
       <c r="AI76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-1400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,200 +7921,206 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E81" s="3">
         <v>-600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-600</v>
       </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
       <c r="J81" s="3">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="K81" s="3">
         <v>-900</v>
       </c>
       <c r="L81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="M81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-12600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
-      </c>
-      <c r="T81" s="3">
-        <v>-1200</v>
       </c>
       <c r="U81" s="3">
         <v>-1200</v>
       </c>
       <c r="V81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="W81" s="3">
         <v>-1000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-600</v>
-      </c>
-      <c r="Z81" s="3">
-        <v>-700</v>
       </c>
       <c r="AA81" s="3">
         <v>-700</v>
       </c>
       <c r="AB81" s="3">
-        <v>-500</v>
+        <v>-700</v>
       </c>
       <c r="AC81" s="3">
         <v>-500</v>
@@ -7934,31 +8129,34 @@
         <v>-500</v>
       </c>
       <c r="AE81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AF81" s="3">
         <v>-800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-300</v>
       </c>
-      <c r="AK81" s="3">
-        <v>0</v>
-      </c>
       <c r="AL81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,8 +8195,9 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8018,11 +8217,11 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
@@ -8030,17 +8229,17 @@
         <v>0</v>
       </c>
       <c r="M83" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N83" s="3">
         <v>300</v>
       </c>
       <c r="O83" s="3">
+        <v>300</v>
+      </c>
+      <c r="P83" s="3">
         <v>200</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -8098,17 +8297,20 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>0</v>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,8 +8871,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8666,109 +8883,112 @@
         <v>4</v>
       </c>
       <c r="E89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F89" s="3">
         <v>600</v>
       </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
       <c r="G89" s="3">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
         <v>400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>100</v>
       </c>
-      <c r="N89" s="3">
-        <v>0</v>
-      </c>
       <c r="O89" s="3">
+        <v>0</v>
+      </c>
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-600</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>-400</v>
       </c>
       <c r="AD89" s="3">
         <v>-400</v>
       </c>
       <c r="AE89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-900</v>
-      </c>
-      <c r="AH89" s="3">
-        <v>-300</v>
       </c>
       <c r="AI89" s="3">
         <v>-300</v>
       </c>
       <c r="AJ89" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="AK89" s="3">
         <v>-100</v>
       </c>
       <c r="AL89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AM89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,16 +9027,17 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
+      <c r="E91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F91" s="3">
         <v>0</v>
@@ -8840,25 +9061,25 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N91" s="3">
         <v>-100</v>
       </c>
       <c r="O91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>4</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>4</v>
@@ -8872,14 +9093,14 @@
       <c r="W91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>4</v>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>4</v>
@@ -8893,8 +9114,8 @@
       <c r="AD91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
+      <c r="AE91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AF91" s="3">
         <v>0</v>
@@ -8917,8 +9138,11 @@
       <c r="AL91" s="3">
         <v>0</v>
       </c>
+      <c r="AM91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,8 +9364,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9152,7 +9382,7 @@
         <v>-200</v>
       </c>
       <c r="G94" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="H94" s="3">
         <v>-100</v>
@@ -9161,43 +9391,43 @@
         <v>-100</v>
       </c>
       <c r="J94" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="K94" s="3">
         <v>-200</v>
       </c>
       <c r="L94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M94" s="3">
         <v>-600</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-100</v>
       </c>
       <c r="N94" s="3">
         <v>-100</v>
       </c>
       <c r="O94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P94" s="3">
         <v>-7600</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3000</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-100</v>
       </c>
       <c r="U94" s="3">
         <v>-100</v>
       </c>
       <c r="V94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -9206,23 +9436,23 @@
         <v>0</v>
       </c>
       <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
       <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-100</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
@@ -9232,14 +9462,14 @@
       <c r="AG94" s="3">
         <v>0</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>4</v>
+      <c r="AH94" s="3">
+        <v>0</v>
       </c>
       <c r="AI94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ94" s="3">
-        <v>0</v>
+      <c r="AJ94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK94" s="3">
         <v>0</v>
@@ -9247,8 +9477,11 @@
       <c r="AL94" s="3">
         <v>0</v>
       </c>
+      <c r="AM94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9319,8 +9553,8 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,8 +9970,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9736,74 +9982,74 @@
         <v>4</v>
       </c>
       <c r="E100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>4500</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>-300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8400</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
         <v>0</v>
       </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>9100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1000</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>500</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
         <v>0</v>
       </c>
@@ -9811,34 +10057,37 @@
         <v>0</v>
       </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>800</v>
-      </c>
-      <c r="AJ100" s="3">
-        <v>100</v>
       </c>
       <c r="AK100" s="3">
         <v>100</v>
       </c>
       <c r="AL100" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9857,8 +10106,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>4</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>4</v>
@@ -9887,8 +10136,8 @@
       <c r="R101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -9947,8 +10196,11 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9956,105 +10208,108 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400</v>
-      </c>
-      <c r="L102" s="3">
-        <v>-300</v>
       </c>
       <c r="M102" s="3">
         <v>-300</v>
       </c>
       <c r="N102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>7400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-200</v>
       </c>
-      <c r="AE102" s="3">
-        <v>0</v>
-      </c>
       <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>1600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>500</v>
       </c>
-      <c r="AJ102" s="3">
-        <v>0</v>
-      </c>
       <c r="AK102" s="3">
         <v>0</v>
       </c>
       <c r="AL102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRME_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>VRME</t>
   </si>
@@ -656,235 +656,242 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F8" s="3">
         <v>5000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>7700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>5400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>5800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>8700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>5300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>5700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>9700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>300</v>
-      </c>
-      <c r="U8" s="3">
-        <v>100</v>
-      </c>
-      <c r="V8" s="3">
-        <v>200</v>
       </c>
       <c r="W8" s="3">
         <v>100</v>
       </c>
       <c r="X8" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y8" s="3">
         <v>100</v>
@@ -899,10 +906,10 @@
         <v>100</v>
       </c>
       <c r="AC8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD8" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE8" s="3">
         <v>0</v>
@@ -913,14 +920,14 @@
       <c r="AG8" s="3">
         <v>0</v>
       </c>
-      <c r="AH8" s="3" t="s">
-        <v>4</v>
+      <c r="AH8" s="3">
+        <v>0</v>
       </c>
       <c r="AI8" s="3">
         <v>0</v>
       </c>
-      <c r="AJ8" s="3">
-        <v>0</v>
+      <c r="AJ8" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AK8" s="3">
         <v>0</v>
@@ -934,68 +941,74 @@
       <c r="AN8" s="3">
         <v>0</v>
       </c>
+      <c r="AO8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>3000</v>
+        <v>800</v>
       </c>
       <c r="E9" s="3">
-        <v>2900</v>
+        <v>1200</v>
       </c>
       <c r="F9" s="3">
         <v>3000</v>
       </c>
       <c r="G9" s="3">
+        <v>2900</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I9" s="3">
         <v>5200</v>
-      </c>
-      <c r="H9" s="3">
-        <v>3500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>3300</v>
       </c>
       <c r="J9" s="3">
         <v>3500</v>
       </c>
       <c r="K9" s="3">
+        <v>3300</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M9" s="3">
         <v>5800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>4100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2800</v>
       </c>
-      <c r="R9" s="3">
-        <v>0</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>100</v>
       </c>
-      <c r="U9" s="3">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3">
-        <v>0</v>
-      </c>
       <c r="W9" s="3">
         <v>0</v>
       </c>
@@ -1029,11 +1042,11 @@
       <c r="AG9" s="3">
         <v>0</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI9" s="3" t="s">
-        <v>4</v>
+      <c r="AH9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3">
+        <v>0</v>
       </c>
       <c r="AJ9" s="3" t="s">
         <v>4</v>
@@ -1044,70 +1057,76 @@
       <c r="AL9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM9" s="3">
-        <v>0</v>
+      <c r="AM9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN9" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F10" s="3">
         <v>2100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>2400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>2100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>2300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>2900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>2000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>2800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1700</v>
-      </c>
-      <c r="R10" s="3">
-        <v>200</v>
-      </c>
-      <c r="S10" s="3">
-        <v>200</v>
       </c>
       <c r="T10" s="3">
         <v>200</v>
       </c>
       <c r="U10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="V10" s="3">
         <v>200</v>
@@ -1116,7 +1135,7 @@
         <v>100</v>
       </c>
       <c r="X10" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="Y10" s="3">
         <v>100</v>
@@ -1131,10 +1150,10 @@
         <v>100</v>
       </c>
       <c r="AC10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD10" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE10" s="3">
         <v>0</v>
@@ -1145,11 +1164,11 @@
       <c r="AG10" s="3">
         <v>0</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI10" s="3" t="s">
-        <v>4</v>
+      <c r="AH10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3">
+        <v>0</v>
       </c>
       <c r="AJ10" s="3" t="s">
         <v>4</v>
@@ -1160,14 +1179,20 @@
       <c r="AL10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AM10" s="3">
-        <v>0</v>
+      <c r="AM10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN10" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,13 +1233,15 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>0</v>
+      <c r="D12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E12" s="3">
         <v>0</v>
@@ -1232,17 +1259,17 @@
         <v>0</v>
       </c>
       <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
-        <v>0</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
       <c r="N12" s="3">
         <v>0</v>
       </c>
@@ -1279,53 +1306,59 @@
       <c r="Y12" s="3">
         <v>0</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>0</v>
+      <c r="Z12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
       </c>
       <c r="AE12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3">
         <v>100</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>100</v>
       </c>
-      <c r="AG12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="3">
-        <v>0</v>
-      </c>
       <c r="AI12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3">
         <v>100</v>
       </c>
-      <c r="AJ12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="3">
-        <v>0</v>
-      </c>
       <c r="AL12" s="3">
         <v>0</v>
       </c>
       <c r="AM12" s="3">
         <v>0</v>
       </c>
-      <c r="AN12" s="3" t="s">
+      <c r="AN12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,70 +1473,76 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>3900</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="3">
-        <v>500</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I14" s="3">
+        <v>200</v>
+      </c>
+      <c r="J14" s="3">
         <v>1800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>300</v>
-      </c>
       <c r="M14" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>300</v>
       </c>
       <c r="O14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="P14" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-300</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
         <v>100</v>
-      </c>
-      <c r="T14" s="3">
-        <v>100</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
       </c>
       <c r="V14" s="3">
         <v>100</v>
       </c>
       <c r="W14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X14" s="3">
         <v>100</v>
@@ -1512,60 +1551,66 @@
         <v>100</v>
       </c>
       <c r="Z14" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="AA14" s="3">
         <v>100</v>
       </c>
       <c r="AB14" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AC14" s="3">
         <v>100</v>
       </c>
       <c r="AD14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="3">
         <v>100</v>
       </c>
       <c r="AF14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG14" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AH14" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3">
         <v>200</v>
       </c>
       <c r="AJ14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL14" s="3">
         <v>100</v>
-      </c>
-      <c r="AK14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AL14" s="3">
-        <v>0</v>
       </c>
       <c r="AM14" s="3">
         <v>100</v>
       </c>
       <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3">
         <v>100</v>
       </c>
+      <c r="AP14" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
         <v>300</v>
@@ -1594,20 +1639,20 @@
       <c r="N15" s="3">
         <v>300</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>4</v>
+      <c r="O15" s="3">
+        <v>300</v>
+      </c>
+      <c r="P15" s="3">
+        <v>300</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="T15" s="3">
         <v>0</v>
@@ -1618,11 +1663,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>4</v>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>4</v>
@@ -1636,11 +1681,11 @@
       <c r="AB15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1672,8 +1717,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1762,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F17" s="3">
         <v>4600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>5000</v>
       </c>
-      <c r="G17" s="3">
-        <v>7700</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>7900</v>
+      </c>
+      <c r="J17" s="3">
         <v>6100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>6400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>8600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>6200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>6400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>6900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>9600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>5800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>1400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>1300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>1500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>1400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>1200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>1100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>1000</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>700</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>700</v>
       </c>
       <c r="AC17" s="3">
         <v>700</v>
       </c>
       <c r="AD17" s="3">
+        <v>700</v>
+      </c>
+      <c r="AE17" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF17" s="3">
         <v>600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>1100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F18" s="3">
         <v>400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
       </c>
       <c r="H18" s="3">
         <v>-600</v>
       </c>
       <c r="I18" s="3">
-        <v>-500</v>
+        <v>-300</v>
       </c>
       <c r="J18" s="3">
         <v>-600</v>
       </c>
       <c r="K18" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="L18" s="3">
         <v>-600</v>
       </c>
       <c r="M18" s="3">
+        <v>100</v>
+      </c>
+      <c r="N18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="O18" s="3">
         <v>-1000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-1200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-1300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-1100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-1400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-1200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-1100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-600</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>-600</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>-700</v>
       </c>
       <c r="AD18" s="3">
         <v>-600</v>
       </c>
       <c r="AE18" s="3">
+        <v>-700</v>
+      </c>
+      <c r="AF18" s="3">
         <v>-600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>-800</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK18" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>-800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>-200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>-1100</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,19 +2050,21 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>4</v>
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -2005,48 +2072,48 @@
       <c r="H20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>4</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-11200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>8200</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
@@ -2054,23 +2121,23 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>0</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
@@ -2080,145 +2147,157 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>4</v>
+      <c r="AH20" s="3">
+        <v>0</v>
       </c>
       <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
         <v>200</v>
       </c>
-      <c r="AL20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3">
         <v>1200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>-1300</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-600</v>
+      </c>
+      <c r="F21" s="3">
         <v>700</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-300</v>
-      </c>
       <c r="G21" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>-300</v>
       </c>
       <c r="I21" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>-300</v>
       </c>
       <c r="K21" s="3">
-        <v>300</v>
+        <v>-200</v>
       </c>
       <c r="L21" s="3">
         <v>-300</v>
       </c>
       <c r="M21" s="3">
+        <v>300</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O21" s="3">
         <v>-800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-12300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-1400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-1000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>7200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-1200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-1100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>-600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>-500</v>
       </c>
       <c r="AF21" s="3">
         <v>-500</v>
       </c>
       <c r="AG21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH21" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI21" s="3">
         <v>-800</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK21" s="3">
         <v>-3100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>-400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>-600</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO21" s="3">
         <v>100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2231,11 +2310,11 @@
       <c r="F22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -2294,11 +2373,11 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>4</v>
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
+        <v>0</v>
       </c>
       <c r="AD22" s="3" t="s">
         <v>4</v>
@@ -2312,11 +2391,11 @@
       <c r="AG22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AH22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>200</v>
+      <c r="AH22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AJ22" s="3">
         <v>0</v>
@@ -2325,132 +2404,144 @@
         <v>200</v>
       </c>
       <c r="AL22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AN22" s="3">
         <v>100</v>
       </c>
-      <c r="AM22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F23" s="3">
         <v>-3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-2400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-600</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-1600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-12600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-1000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>7200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-1400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-1200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-1200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD23" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AE23" s="3">
-        <v>-500</v>
       </c>
       <c r="AF23" s="3">
         <v>-500</v>
       </c>
       <c r="AG23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH23" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>-800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>-300</v>
       </c>
-      <c r="AM23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2499,17 +2590,17 @@
       <c r="R24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>4</v>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>4</v>
@@ -2523,11 +2614,11 @@
       <c r="Z24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>0</v>
+      <c r="AA24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC24" s="3">
         <v>0</v>
@@ -2565,8 +2656,14 @@
       <c r="AN24" s="3">
         <v>0</v>
       </c>
+      <c r="AO24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2778,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-2400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-600</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-1600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-12600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>7200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-1400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-1200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD26" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AE26" s="3">
-        <v>-500</v>
       </c>
       <c r="AF26" s="3">
         <v>-500</v>
       </c>
       <c r="AG26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI26" s="3">
         <v>-800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>-800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>-300</v>
       </c>
-      <c r="AM26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP26" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-2400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-600</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-12600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>7200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-1400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-1200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD27" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AE27" s="3">
-        <v>-500</v>
       </c>
       <c r="AF27" s="3">
         <v>-500</v>
       </c>
       <c r="AG27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI27" s="3">
         <v>-800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>-300</v>
       </c>
-      <c r="AM27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP27" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3266,14 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,19 +3510,25 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>4</v>
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -3397,48 +3536,48 @@
       <c r="H32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>4</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>11200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-8200</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3446,23 +3585,23 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>1900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
@@ -3472,145 +3611,157 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>4</v>
+      <c r="AH32" s="3">
+        <v>0</v>
       </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK32" s="3">
         <v>300</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
         <v>-200</v>
       </c>
-      <c r="AL32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-2400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-600</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-12600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>7200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-1200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD33" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AE33" s="3">
-        <v>-500</v>
       </c>
       <c r="AF33" s="3">
         <v>-500</v>
       </c>
       <c r="AG33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI33" s="3">
         <v>-800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>-300</v>
       </c>
-      <c r="AM33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP33" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3876,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-2400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-600</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-12600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>7200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-1200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD35" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AE35" s="3">
-        <v>-500</v>
       </c>
       <c r="AF35" s="3">
         <v>-500</v>
       </c>
       <c r="AG35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI35" s="3">
         <v>-800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>-300</v>
       </c>
-      <c r="AM35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP35" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4217,132 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F41" s="3">
         <v>4000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>6100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>5700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>3000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>3100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>3800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>8400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>9400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>10600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>11400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>15400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>7900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>9000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>9600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>1100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>1700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>2100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>2300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>2300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>500</v>
       </c>
-      <c r="AL41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM41" s="3">
-        <v>0</v>
-      </c>
       <c r="AN41" s="3">
         <v>0</v>
       </c>
+      <c r="AO41" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP41" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4192,31 +4371,31 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>100</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>4</v>
+      <c r="O42" s="3">
+        <v>0</v>
       </c>
       <c r="P42" s="3">
-        <v>100</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R42" s="3">
         <v>100</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>4</v>
+      <c r="S42" s="3">
+        <v>100</v>
+      </c>
+      <c r="T42" s="3">
+        <v>100</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>4</v>
@@ -4227,11 +4406,11 @@
       <c r="W42" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y42" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -4278,73 +4457,79 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F43" s="3">
         <v>3500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>4300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>5600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>3100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>200</v>
-      </c>
-      <c r="W43" s="3">
-        <v>0</v>
-      </c>
-      <c r="X43" s="3">
-        <v>100</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -4353,16 +4538,16 @@
         <v>100</v>
       </c>
       <c r="AA43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="3">
         <v>100</v>
       </c>
       <c r="AC43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
@@ -4373,11 +4558,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI43" s="3" t="s">
-        <v>4</v>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="3">
+        <v>0</v>
       </c>
       <c r="AJ43" s="3" t="s">
         <v>4</v>
@@ -4394,8 +4579,14 @@
       <c r="AN43" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="AO43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP43" s="3" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4430,10 +4621,10 @@
         <v>0</v>
       </c>
       <c r="N44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O44" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P44" s="3">
         <v>100</v>
@@ -4448,7 +4639,7 @@
         <v>100</v>
       </c>
       <c r="T44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U44" s="3">
         <v>100</v>
@@ -4463,7 +4654,7 @@
         <v>0</v>
       </c>
       <c r="Y44" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
@@ -4508,10 +4699,16 @@
         <v>0</v>
       </c>
       <c r="AN44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP44" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4548,59 +4745,59 @@
       <c r="N45" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>300</v>
       </c>
       <c r="S45" s="3">
         <v>200</v>
       </c>
       <c r="T45" s="3">
+        <v>300</v>
+      </c>
+      <c r="U45" s="3">
+        <v>200</v>
+      </c>
+      <c r="V45" s="3">
         <v>100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>100</v>
       </c>
-      <c r="Y45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
         <v>100</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>200</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>200</v>
       </c>
       <c r="AD45" s="3">
         <v>200</v>
       </c>
       <c r="AE45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AF45" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AG45" s="3">
         <v>0</v>
@@ -4623,127 +4820,139 @@
       <c r="AM45" s="3">
         <v>0</v>
       </c>
-      <c r="AN45" s="3" t="s">
+      <c r="AN45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP45" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F46" s="3">
         <v>7900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>7900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>7700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>6400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>7700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>9500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>6000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>6500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>9100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>10000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>11100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>14600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>15800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>8200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>9200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>9700</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AA46" s="3">
-        <v>400</v>
       </c>
       <c r="AB46" s="3">
         <v>1000</v>
       </c>
       <c r="AC46" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD46" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE46" s="3">
         <v>800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>2200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>2400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>2400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>600</v>
       </c>
-      <c r="AL46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM46" s="3">
-        <v>0</v>
-      </c>
       <c r="AN46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP46" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4780,32 +4989,32 @@
       <c r="N47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>11200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>11000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>10800</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="W47" s="3" t="s">
-        <v>4</v>
+      <c r="W47" s="3">
+        <v>0</v>
       </c>
       <c r="X47" s="3" t="s">
         <v>4</v>
@@ -4819,11 +5028,11 @@
       <c r="AA47" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -4858,58 +5067,64 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3">
         <v>100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>800</v>
-      </c>
-      <c r="M48" s="3">
-        <v>800</v>
-      </c>
-      <c r="N48" s="3">
-        <v>900</v>
       </c>
       <c r="O48" s="3">
         <v>800</v>
       </c>
       <c r="P48" s="3">
+        <v>900</v>
+      </c>
+      <c r="Q48" s="3">
         <v>800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
+        <v>800</v>
+      </c>
+      <c r="S48" s="3">
         <v>900</v>
-      </c>
-      <c r="R48" s="3">
-        <v>200</v>
-      </c>
-      <c r="S48" s="3">
-        <v>200</v>
       </c>
       <c r="T48" s="3">
         <v>200</v>
@@ -4935,11 +5150,11 @@
       <c r="AA48" s="3">
         <v>200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC48" s="3" t="s">
-        <v>4</v>
+      <c r="AB48" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>200</v>
       </c>
       <c r="AD48" s="3" t="s">
         <v>4</v>
@@ -4959,11 +5174,11 @@
       <c r="AI48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AJ48" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK48" s="3">
-        <v>0</v>
+      <c r="AJ48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AL48" s="3">
         <v>0</v>
@@ -4974,58 +5189,64 @@
       <c r="AN48" s="3">
         <v>0</v>
       </c>
+      <c r="AO48" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F49" s="3">
         <v>5200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>9000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>9100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>9200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>9400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>11700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>11900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>12100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>12200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>12300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>12500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>10400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>10500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>10600</v>
-      </c>
-      <c r="R49" s="3">
-        <v>500</v>
-      </c>
-      <c r="S49" s="3">
-        <v>500</v>
       </c>
       <c r="T49" s="3">
         <v>500</v>
@@ -5034,16 +5255,16 @@
         <v>500</v>
       </c>
       <c r="V49" s="3">
+        <v>500</v>
+      </c>
+      <c r="W49" s="3">
+        <v>500</v>
+      </c>
+      <c r="X49" s="3">
         <v>400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>400</v>
-      </c>
-      <c r="X49" s="3">
-        <v>300</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>300</v>
       </c>
       <c r="Z49" s="3">
         <v>300</v>
@@ -5052,22 +5273,22 @@
         <v>300</v>
       </c>
       <c r="AB49" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AC49" s="3">
         <v>300</v>
       </c>
       <c r="AD49" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AE49" s="3">
         <v>300</v>
       </c>
       <c r="AF49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AG49" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AH49" s="3">
         <v>200</v>
@@ -5090,8 +5311,14 @@
       <c r="AN49" s="3">
         <v>200</v>
       </c>
+      <c r="AO49" s="3">
+        <v>200</v>
+      </c>
+      <c r="AP49" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,8 +5555,14 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5360,20 +5599,20 @@
       <c r="N52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O52" s="3">
-        <v>100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>100</v>
+      <c r="O52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
+      <c r="R52" s="3">
+        <v>100</v>
+      </c>
+      <c r="S52" s="3">
+        <v>100</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
@@ -5387,11 +5626,11 @@
       <c r="W52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
@@ -5438,8 +5677,14 @@
       <c r="AN52" s="3">
         <v>0</v>
       </c>
+      <c r="AO52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>13000</v>
+      </c>
+      <c r="F54" s="3">
         <v>13300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>17200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>17100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>16100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>14800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>17500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>17900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>20700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>18800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>18400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>19400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>20800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>17400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>18100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>20900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>21700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>22600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>15300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>16500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>8800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>9800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>10300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>2100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>2400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>2500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>2600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>800</v>
-      </c>
-      <c r="AL54" s="3">
-        <v>300</v>
-      </c>
-      <c r="AM54" s="3">
-        <v>300</v>
       </c>
       <c r="AN54" s="3">
         <v>300</v>
       </c>
+      <c r="AO54" s="3">
+        <v>300</v>
+      </c>
+      <c r="AP54" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,64 +6013,66 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>1000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>500</v>
-      </c>
-      <c r="T57" s="3">
-        <v>400</v>
-      </c>
-      <c r="U57" s="3">
-        <v>400</v>
       </c>
       <c r="V57" s="3">
         <v>400</v>
@@ -5820,13 +6081,13 @@
         <v>400</v>
       </c>
       <c r="X57" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y57" s="3">
         <v>400</v>
       </c>
       <c r="Z57" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AA57" s="3">
         <v>400</v>
@@ -5850,13 +6111,13 @@
         <v>400</v>
       </c>
       <c r="AH57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI57" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>500</v>
-      </c>
-      <c r="AI57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="AJ57" s="3">
-        <v>900</v>
       </c>
       <c r="AK57" s="3">
         <v>1000</v>
@@ -5865,13 +6126,19 @@
         <v>900</v>
       </c>
       <c r="AM57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AN57" s="3">
         <v>900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
+        <v>900</v>
+      </c>
+      <c r="AP57" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5879,19 +6146,19 @@
         <v>800</v>
       </c>
       <c r="E58" s="3">
+        <v>800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>800</v>
+      </c>
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>600</v>
-      </c>
-      <c r="H58" s="3">
-        <v>700</v>
-      </c>
-      <c r="I58" s="3">
-        <v>700</v>
       </c>
       <c r="J58" s="3">
         <v>700</v>
@@ -5900,28 +6167,28 @@
         <v>700</v>
       </c>
       <c r="L58" s="3">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M58" s="3">
-        <v>1500</v>
+        <v>700</v>
       </c>
       <c r="N58" s="3">
         <v>1200</v>
       </c>
       <c r="O58" s="3">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="P58" s="3">
-        <v>500</v>
+        <v>1200</v>
       </c>
       <c r="Q58" s="3">
         <v>500</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>4</v>
+      <c r="R58" s="3">
+        <v>500</v>
+      </c>
+      <c r="S58" s="3">
+        <v>500</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>4</v>
@@ -5932,11 +6199,11 @@
       <c r="V58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -5945,28 +6212,28 @@
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
         <v>300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>200</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD58" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>0</v>
+      <c r="AE58" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AG58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI58" s="3">
         <v>100</v>
@@ -5978,16 +6245,22 @@
         <v>100</v>
       </c>
       <c r="AL58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AM58" s="3">
         <v>100</v>
       </c>
       <c r="AN58" s="3">
+        <v>200</v>
+      </c>
+      <c r="AO58" s="3">
         <v>100</v>
       </c>
+      <c r="AP58" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6003,42 +6276,42 @@
       <c r="G59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>200</v>
-      </c>
-      <c r="K59" s="3">
-        <v>200</v>
       </c>
       <c r="L59" s="3">
         <v>200</v>
       </c>
       <c r="M59" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N59" s="3">
         <v>200</v>
       </c>
       <c r="O59" s="3">
+        <v>100</v>
+      </c>
+      <c r="P59" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>4</v>
       </c>
@@ -6048,118 +6321,124 @@
       <c r="V59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3">
-        <v>0</v>
+      <c r="W59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Y59" s="3">
         <v>0</v>
       </c>
       <c r="Z59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="3">
         <v>100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>300</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>100</v>
-      </c>
-      <c r="AD59" s="3">
-        <v>100</v>
       </c>
       <c r="AE59" s="3">
         <v>100</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG59" s="3" t="s">
-        <v>4</v>
+      <c r="AF59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG59" s="3">
+        <v>100</v>
       </c>
       <c r="AH59" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AI59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="3">
+      <c r="AI59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="3">
         <v>100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>100</v>
-      </c>
-      <c r="AL59" s="3">
-        <v>700</v>
-      </c>
-      <c r="AM59" s="3">
-        <v>600</v>
       </c>
       <c r="AN59" s="3">
         <v>700</v>
       </c>
+      <c r="AO59" s="3">
+        <v>600</v>
+      </c>
+      <c r="AP59" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>4200</v>
-      </c>
-      <c r="H60" s="3">
-        <v>2800</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2900</v>
       </c>
       <c r="J60" s="3">
         <v>2800</v>
       </c>
       <c r="K60" s="3">
+        <v>2900</v>
+      </c>
+      <c r="L60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M60" s="3">
         <v>5100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>5400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>2300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>500</v>
-      </c>
-      <c r="T60" s="3">
-        <v>400</v>
-      </c>
-      <c r="U60" s="3">
-        <v>400</v>
       </c>
       <c r="V60" s="3">
         <v>400</v>
@@ -6168,58 +6447,64 @@
         <v>400</v>
       </c>
       <c r="X60" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="Y60" s="3">
         <v>400</v>
       </c>
       <c r="Z60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AA60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB60" s="3">
         <v>600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>500</v>
-      </c>
-      <c r="AE60" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF60" s="3">
-        <v>400</v>
       </c>
       <c r="AG60" s="3">
         <v>500</v>
       </c>
       <c r="AH60" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI60" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ60" s="3">
         <v>600</v>
-      </c>
-      <c r="AI60" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AJ60" s="3">
-        <v>1000</v>
       </c>
       <c r="AK60" s="3">
         <v>1100</v>
       </c>
       <c r="AL60" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AM60" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AN60" s="3">
         <v>1700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>1600</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6227,50 +6512,50 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1500</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -6278,10 +6563,10 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X61" s="3">
         <v>100</v>
@@ -6293,10 +6578,10 @@
         <v>100</v>
       </c>
       <c r="AA61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC61" s="3">
         <v>0</v>
@@ -6334,8 +6619,14 @@
       <c r="AN61" s="3">
         <v>0</v>
       </c>
+      <c r="AO61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6354,47 +6645,47 @@
       <c r="H62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>800</v>
-      </c>
-      <c r="L62" s="3">
-        <v>800</v>
       </c>
       <c r="M62" s="3">
         <v>800</v>
       </c>
       <c r="N62" s="3">
+        <v>800</v>
+      </c>
+      <c r="O62" s="3">
+        <v>800</v>
+      </c>
+      <c r="P62" s="3">
         <v>1000</v>
-      </c>
-      <c r="O62" s="3">
-        <v>400</v>
-      </c>
-      <c r="P62" s="3">
-        <v>400</v>
       </c>
       <c r="Q62" s="3">
         <v>400</v>
       </c>
       <c r="R62" s="3">
+        <v>400</v>
+      </c>
+      <c r="S62" s="3">
+        <v>400</v>
+      </c>
+      <c r="T62" s="3">
         <v>100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>100</v>
       </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>4</v>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>4</v>
@@ -6408,11 +6699,11 @@
       <c r="Z62" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
@@ -6444,14 +6735,20 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
-      <c r="AM62" s="3" t="s">
-        <v>4</v>
+      <c r="AM62" s="3">
+        <v>0</v>
       </c>
       <c r="AN62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP62" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7107,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F66" s="3">
         <v>2200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>8200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>6900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>6100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>6400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>7200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>500</v>
-      </c>
-      <c r="W66" s="3">
-        <v>500</v>
-      </c>
-      <c r="X66" s="3">
-        <v>600</v>
       </c>
       <c r="Y66" s="3">
         <v>500</v>
       </c>
       <c r="Z66" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA66" s="3">
+        <v>500</v>
+      </c>
+      <c r="AB66" s="3">
         <v>700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>500</v>
-      </c>
-      <c r="AE66" s="3">
-        <v>500</v>
-      </c>
-      <c r="AF66" s="3">
-        <v>400</v>
       </c>
       <c r="AG66" s="3">
         <v>500</v>
       </c>
       <c r="AH66" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI66" s="3">
+        <v>500</v>
+      </c>
+      <c r="AJ66" s="3">
         <v>600</v>
-      </c>
-      <c r="AI66" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AJ66" s="3">
-        <v>1000</v>
       </c>
       <c r="AK66" s="3">
         <v>1100</v>
       </c>
       <c r="AL66" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AM66" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AN66" s="3">
         <v>1700</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>1600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7761,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-91300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-90600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-89900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-86500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-86200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-85700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-85200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-82700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-82400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-81800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-81900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-80900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-80000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-78500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-78600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-78000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-65500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-64100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-63100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-70200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-68900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-67700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-66500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-65500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-62900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-61800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-61100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-60400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-59800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>-59300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-58700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>-58200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>-57500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>-56300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>-42800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>-42500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>-41900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>-41600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>11000</v>
+      </c>
+      <c r="F76" s="3">
         <v>11100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>14400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>14600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>10200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>10300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>12300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>12400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>12500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>11900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13000</v>
-      </c>
-      <c r="O76" s="3">
-        <v>13600</v>
-      </c>
-      <c r="P76" s="3">
-        <v>13200</v>
       </c>
       <c r="Q76" s="3">
         <v>13600</v>
       </c>
       <c r="R76" s="3">
+        <v>13200</v>
+      </c>
+      <c r="S76" s="3">
+        <v>13600</v>
+      </c>
+      <c r="T76" s="3">
         <v>20200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>21200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>22200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>14900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>16000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>8300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>9100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>9800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>-100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>1100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>1600</v>
-      </c>
-      <c r="AF76" s="3">
-        <v>2000</v>
-      </c>
-      <c r="AG76" s="3">
-        <v>2000</v>
       </c>
       <c r="AH76" s="3">
         <v>2000</v>
       </c>
       <c r="AI76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AJ76" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AK76" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="3">
         <v>-300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>-1400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>-1300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>-2200</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8493,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-2400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-600</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-12600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>7200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-1200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD81" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AE81" s="3">
-        <v>-500</v>
       </c>
       <c r="AF81" s="3">
         <v>-500</v>
       </c>
       <c r="AG81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH81" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AI81" s="3">
         <v>-800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>-300</v>
       </c>
-      <c r="AM81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP81" s="3">
         <v>-1800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,8 +8790,10 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8422,32 +8819,32 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
       <c r="O83" s="3">
+        <v>0</v>
+      </c>
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
         <v>300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -8502,17 +8899,23 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>4</v>
+      <c r="AL83" s="3">
+        <v>0</v>
       </c>
       <c r="AM83" s="3">
         <v>0</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AN83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP83" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>600</v>
       </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>400</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K89" s="3">
-        <v>800</v>
       </c>
       <c r="L89" s="3">
         <v>-100</v>
       </c>
       <c r="M89" s="3">
-        <v>-300</v>
+        <v>800</v>
       </c>
       <c r="N89" s="3">
         <v>-100</v>
       </c>
       <c r="O89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q89" s="3">
         <v>100</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-1000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>-200</v>
       </c>
       <c r="AB89" s="3">
         <v>-300</v>
       </c>
       <c r="AC89" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="AD89" s="3">
-        <v>-600</v>
+        <v>-300</v>
       </c>
       <c r="AE89" s="3">
         <v>-400</v>
       </c>
       <c r="AF89" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AI89" s="3">
         <v>-600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>-300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>-300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>-100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>-100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,25 +9688,27 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>4</v>
+      <c r="F91" s="3">
+        <v>0</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
@@ -9288,28 +9729,28 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>4</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>4</v>
@@ -9320,17 +9761,17 @@
       <c r="Y91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC91" s="3" t="s">
-        <v>4</v>
+      <c r="Z91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>4</v>
@@ -9341,11 +9782,11 @@
       <c r="AF91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>0</v>
+      <c r="AG91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AI91" s="3">
         <v>0</v>
@@ -9365,8 +9806,14 @@
       <c r="AN91" s="3">
         <v>0</v>
       </c>
+      <c r="AO91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,19 +10050,25 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2200</v>
+        <v>-100</v>
       </c>
       <c r="E94" s="3">
         <v>-200</v>
       </c>
       <c r="F94" s="3">
-        <v>-200</v>
+        <v>-2200</v>
       </c>
       <c r="G94" s="3">
         <v>-200</v>
@@ -9618,67 +10077,67 @@
         <v>-200</v>
       </c>
       <c r="I94" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="J94" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="K94" s="3">
         <v>-100</v>
       </c>
       <c r="L94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-7600</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-200</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-100</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -9690,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="AG94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AH94" s="3">
         <v>0</v>
@@ -9698,23 +10157,29 @@
       <c r="AI94" s="3">
         <v>0</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM94" s="3">
-        <v>0</v>
+      <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="AN94" s="3">
         <v>0</v>
       </c>
+      <c r="AO94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +10220,10 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9793,11 +10260,11 @@
       <c r="N96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9871,8 +10338,14 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,25 +10704,31 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-100</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F100" s="3">
-        <v>3400</v>
       </c>
       <c r="G100" s="3">
         <v>-200</v>
       </c>
       <c r="H100" s="3">
-        <v>-100</v>
+        <v>3400</v>
       </c>
       <c r="I100" s="3">
         <v>-200</v>
@@ -10246,102 +10737,108 @@
         <v>-100</v>
       </c>
       <c r="K100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
         <v>-600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>4500</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>-300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>8400</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>9100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>1000</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>500</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>2600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
@@ -10361,11 +10858,11 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>4</v>
@@ -10391,11 +10888,11 @@
       <c r="T101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -10451,28 +10948,34 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>2900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>200</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>100</v>
       </c>
       <c r="J102" s="3">
         <v>-300</v>
@@ -10481,90 +10984,96 @@
         <v>100</v>
       </c>
       <c r="L102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M102" s="3">
+        <v>100</v>
+      </c>
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-4700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-1000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-4000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>7400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-1000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>8700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
-      </c>
-      <c r="AC102" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>-600</v>
       </c>
       <c r="AE102" s="3">
         <v>-500</v>
       </c>
       <c r="AF102" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AG102" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
-      <c r="AG102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>1600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>500</v>
       </c>
-      <c r="AL102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM102" s="3">
-        <v>0</v>
-      </c>
       <c r="AN102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP102" s="3">
         <v>-200</v>
       </c>
     </row>
